--- a/grupos/4APV - Estadisticos 20222.xlsx
+++ b/grupos/4APV - Estadisticos 20222.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="125">
   <si>
     <t>Materia</t>
   </si>
@@ -204,6 +204,15 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>SARMIENTO</t>
+  </si>
+  <si>
+    <t>JESUS</t>
+  </si>
+  <si>
     <t>BARRAGAN</t>
   </si>
   <si>
@@ -231,9 +240,6 @@
     <t>GOMEZ</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
     <t>LIBRADO</t>
   </si>
   <si>
@@ -294,9 +300,6 @@
     <t>CAPORAL</t>
   </si>
   <si>
-    <t>SARMIENTO</t>
-  </si>
-  <si>
     <t>CORONADO</t>
   </si>
   <si>
@@ -358,9 +361,6 @@
   </si>
   <si>
     <t>CLAUDIA</t>
-  </si>
-  <si>
-    <t>JESUS</t>
   </si>
   <si>
     <t>LIZBETH</t>
@@ -907,7 +907,7 @@
         <v>10</v>
       </c>
       <c r="F4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G4">
         <v>10</v>
@@ -970,7 +970,7 @@
         <v>10</v>
       </c>
       <c r="AA4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AB4">
         <v>10</v>
@@ -996,7 +996,7 @@
         <v>6</v>
       </c>
       <c r="F5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -1059,7 +1059,7 @@
         <v>6</v>
       </c>
       <c r="AA5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AB5">
         <v>5</v>
@@ -1085,7 +1085,7 @@
         <v>5</v>
       </c>
       <c r="F6">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -1148,7 +1148,7 @@
         <v>5</v>
       </c>
       <c r="AA6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AB6">
         <v>5</v>
@@ -1174,7 +1174,7 @@
         <v>9</v>
       </c>
       <c r="F7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G7">
         <v>6</v>
@@ -1237,7 +1237,7 @@
         <v>9</v>
       </c>
       <c r="AA7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AB7">
         <v>6</v>
@@ -1263,7 +1263,7 @@
         <v>5</v>
       </c>
       <c r="F8">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -1326,7 +1326,7 @@
         <v>5</v>
       </c>
       <c r="AA8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AB8">
         <v>5</v>
@@ -1352,7 +1352,7 @@
         <v>10</v>
       </c>
       <c r="F9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G9">
         <v>6</v>
@@ -1415,7 +1415,7 @@
         <v>10</v>
       </c>
       <c r="AA9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB9">
         <v>6</v>
@@ -1441,7 +1441,7 @@
         <v>5</v>
       </c>
       <c r="F10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -1504,7 +1504,7 @@
         <v>5</v>
       </c>
       <c r="AA10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AB10">
         <v>5</v>
@@ -1530,7 +1530,7 @@
         <v>9</v>
       </c>
       <c r="F11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G11">
         <v>6</v>
@@ -1593,7 +1593,7 @@
         <v>9</v>
       </c>
       <c r="AA11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AB11">
         <v>6</v>
@@ -1619,7 +1619,7 @@
         <v>8</v>
       </c>
       <c r="F12">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="G12">
         <v>8</v>
@@ -1682,7 +1682,7 @@
         <v>8</v>
       </c>
       <c r="AA12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AB12">
         <v>8</v>
@@ -1708,7 +1708,7 @@
         <v>9</v>
       </c>
       <c r="F13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G13">
         <v>10</v>
@@ -1771,7 +1771,7 @@
         <v>9</v>
       </c>
       <c r="AA13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AB13">
         <v>10</v>
@@ -1797,7 +1797,7 @@
         <v>5</v>
       </c>
       <c r="F14">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="G14">
         <v>5</v>
@@ -1860,7 +1860,7 @@
         <v>5</v>
       </c>
       <c r="AA14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AB14">
         <v>5</v>
@@ -1886,7 +1886,7 @@
         <v>10</v>
       </c>
       <c r="F15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G15">
         <v>5</v>
@@ -1949,7 +1949,7 @@
         <v>10</v>
       </c>
       <c r="AA15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AB15">
         <v>5</v>
@@ -1975,7 +1975,7 @@
         <v>7</v>
       </c>
       <c r="F16">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="G16">
         <v>5</v>
@@ -2038,7 +2038,7 @@
         <v>7</v>
       </c>
       <c r="AA16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AB16">
         <v>5</v>
@@ -2064,7 +2064,7 @@
         <v>7</v>
       </c>
       <c r="F17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G17">
         <v>6</v>
@@ -2127,7 +2127,7 @@
         <v>7</v>
       </c>
       <c r="AA17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AB17">
         <v>6</v>
@@ -2230,7 +2230,7 @@
         <v>10</v>
       </c>
       <c r="F19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G19">
         <v>6</v>
@@ -2293,7 +2293,7 @@
         <v>10</v>
       </c>
       <c r="AA19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AB19">
         <v>6</v>
@@ -2319,7 +2319,7 @@
         <v>5</v>
       </c>
       <c r="F20">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="G20">
         <v>5</v>
@@ -2382,7 +2382,7 @@
         <v>5</v>
       </c>
       <c r="AA20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AB20">
         <v>5</v>
@@ -2408,7 +2408,7 @@
         <v>8</v>
       </c>
       <c r="F21">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="G21">
         <v>5</v>
@@ -2471,7 +2471,7 @@
         <v>8</v>
       </c>
       <c r="AA21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AB21">
         <v>5</v>
@@ -2497,7 +2497,7 @@
         <v>5</v>
       </c>
       <c r="F22">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="G22">
         <v>5</v>
@@ -2560,7 +2560,7 @@
         <v>5</v>
       </c>
       <c r="AA22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AB22">
         <v>5</v>
@@ -2586,7 +2586,7 @@
         <v>5</v>
       </c>
       <c r="F23">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="G23">
         <v>6</v>
@@ -2649,7 +2649,7 @@
         <v>5</v>
       </c>
       <c r="AA23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AB23">
         <v>6</v>
@@ -2675,7 +2675,7 @@
         <v>6</v>
       </c>
       <c r="F24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G24">
         <v>6</v>
@@ -2738,7 +2738,7 @@
         <v>6</v>
       </c>
       <c r="AA24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AB24">
         <v>6</v>
@@ -2764,7 +2764,7 @@
         <v>8</v>
       </c>
       <c r="F25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G25">
         <v>6</v>
@@ -2827,7 +2827,7 @@
         <v>8</v>
       </c>
       <c r="AA25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AB25">
         <v>6</v>
@@ -2853,7 +2853,7 @@
         <v>10</v>
       </c>
       <c r="F26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G26">
         <v>6</v>
@@ -2916,7 +2916,7 @@
         <v>10</v>
       </c>
       <c r="AA26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AB26">
         <v>6</v>
@@ -2942,7 +2942,7 @@
         <v>6</v>
       </c>
       <c r="F27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G27">
         <v>7</v>
@@ -3005,7 +3005,7 @@
         <v>6</v>
       </c>
       <c r="AA27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AB27">
         <v>7</v>
@@ -3031,7 +3031,7 @@
         <v>5</v>
       </c>
       <c r="F28">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="G28">
         <v>5</v>
@@ -3094,7 +3094,7 @@
         <v>5</v>
       </c>
       <c r="AA28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AB28">
         <v>5</v>
@@ -3242,7 +3242,7 @@
         <v>100</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="G4">
         <v>100</v>
@@ -3310,7 +3310,7 @@
         <v>86.7</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G5">
         <v>100</v>
@@ -3378,7 +3378,7 @@
         <v>63.3</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="G6">
         <v>70</v>
@@ -3446,7 +3446,7 @@
         <v>83.3</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="G7">
         <v>100</v>
@@ -3514,7 +3514,7 @@
         <v>63.3</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="G8">
         <v>85</v>
@@ -3582,7 +3582,7 @@
         <v>96.7</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G9">
         <v>100</v>
@@ -3650,7 +3650,7 @@
         <v>83.3</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G10">
         <v>90</v>
@@ -3718,7 +3718,7 @@
         <v>100</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="G11">
         <v>100</v>
@@ -3786,7 +3786,7 @@
         <v>73.3</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="G12">
         <v>70</v>
@@ -3854,7 +3854,7 @@
         <v>100</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G13">
         <v>85</v>
@@ -3922,7 +3922,7 @@
         <v>63.3</v>
       </c>
       <c r="F14">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="G14">
         <v>85</v>
@@ -3990,7 +3990,7 @@
         <v>86.7</v>
       </c>
       <c r="F15">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="G15">
         <v>100</v>
@@ -4058,7 +4058,7 @@
         <v>66.7</v>
       </c>
       <c r="F16">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="G16">
         <v>85</v>
@@ -4126,7 +4126,7 @@
         <v>100</v>
       </c>
       <c r="F17">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="G17">
         <v>100</v>
@@ -4253,7 +4253,7 @@
         <v>93.3</v>
       </c>
       <c r="F19">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="G19">
         <v>95</v>
@@ -4321,7 +4321,7 @@
         <v>83.3</v>
       </c>
       <c r="F20">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="G20">
         <v>75</v>
@@ -4389,7 +4389,7 @@
         <v>86.7</v>
       </c>
       <c r="F21">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="G21">
         <v>90</v>
@@ -4457,7 +4457,7 @@
         <v>66.7</v>
       </c>
       <c r="F22">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="G22">
         <v>75</v>
@@ -4525,7 +4525,7 @@
         <v>76.7</v>
       </c>
       <c r="F23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G23">
         <v>85</v>
@@ -4593,7 +4593,7 @@
         <v>66.7</v>
       </c>
       <c r="F24">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="G24">
         <v>85</v>
@@ -4661,7 +4661,7 @@
         <v>93.3</v>
       </c>
       <c r="F25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G25">
         <v>90</v>
@@ -4729,7 +4729,7 @@
         <v>90</v>
       </c>
       <c r="F26">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="G26">
         <v>100</v>
@@ -4797,7 +4797,7 @@
         <v>100</v>
       </c>
       <c r="F27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G27">
         <v>100</v>
@@ -4865,7 +4865,7 @@
         <v>66.7</v>
       </c>
       <c r="F28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G28">
         <v>85</v>
@@ -4977,22 +4977,25 @@
         <v>25</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>60</v>
+      </c>
+      <c r="H2">
+        <v>6.1</v>
       </c>
       <c r="I2">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="J2">
-        <v>100</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -5194,7 +5197,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5223,498 +5226,21 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>21330051920111</v>
+        <v>20330051920346</v>
       </c>
       <c r="B2" t="s">
         <v>61</v>
       </c>
       <c r="C2" t="s">
-        <v>81</v>
+        <v>62</v>
       </c>
       <c r="D2" t="s">
-        <v>101</v>
+        <v>63</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>21330051920112</v>
-      </c>
-      <c r="B3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C3" t="s">
-        <v>82</v>
-      </c>
-      <c r="D3" t="s">
-        <v>102</v>
-      </c>
-      <c r="E3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>21330051920113</v>
-      </c>
-      <c r="B4" t="s">
-        <v>63</v>
-      </c>
-      <c r="C4" t="s">
-        <v>70</v>
-      </c>
-      <c r="D4" t="s">
-        <v>103</v>
-      </c>
-      <c r="E4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>21330051920114</v>
-      </c>
-      <c r="B5" t="s">
-        <v>64</v>
-      </c>
-      <c r="C5" t="s">
-        <v>83</v>
-      </c>
-      <c r="D5" t="s">
-        <v>104</v>
-      </c>
-      <c r="E5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>21330051920116</v>
-      </c>
-      <c r="B6" t="s">
-        <v>65</v>
-      </c>
-      <c r="C6" t="s">
-        <v>84</v>
-      </c>
-      <c r="D6" t="s">
-        <v>105</v>
-      </c>
-      <c r="E6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>21330051920117</v>
-      </c>
-      <c r="B7" t="s">
-        <v>66</v>
-      </c>
-      <c r="C7" t="s">
-        <v>85</v>
-      </c>
-      <c r="D7" t="s">
-        <v>106</v>
-      </c>
-      <c r="E7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>21330051920118</v>
-      </c>
-      <c r="B8" t="s">
-        <v>67</v>
-      </c>
-      <c r="C8" t="s">
-        <v>86</v>
-      </c>
-      <c r="D8" t="s">
-        <v>102</v>
-      </c>
-      <c r="E8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>21330051920119</v>
-      </c>
-      <c r="B9" t="s">
-        <v>68</v>
-      </c>
-      <c r="C9" t="s">
-        <v>87</v>
-      </c>
-      <c r="D9" t="s">
-        <v>107</v>
-      </c>
-      <c r="E9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>20330051920266</v>
-      </c>
-      <c r="B10" t="s">
-        <v>68</v>
-      </c>
-      <c r="C10" t="s">
-        <v>88</v>
-      </c>
-      <c r="D10" t="s">
-        <v>108</v>
-      </c>
-      <c r="E10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>21330051920120</v>
-      </c>
-      <c r="B11" t="s">
-        <v>68</v>
-      </c>
-      <c r="C11" t="s">
-        <v>89</v>
-      </c>
-      <c r="D11" t="s">
-        <v>109</v>
-      </c>
-      <c r="E11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>21330051920121</v>
-      </c>
-      <c r="B12" t="s">
-        <v>68</v>
-      </c>
-      <c r="C12" t="s">
-        <v>82</v>
-      </c>
-      <c r="D12" t="s">
-        <v>110</v>
-      </c>
-      <c r="E12" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>21330051920391</v>
-      </c>
-      <c r="B13" t="s">
-        <v>69</v>
-      </c>
-      <c r="C13" t="s">
-        <v>90</v>
-      </c>
-      <c r="D13" t="s">
-        <v>111</v>
-      </c>
-      <c r="E13" t="s">
-        <v>9</v>
-      </c>
-      <c r="F13" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>21330051920122</v>
-      </c>
-      <c r="B14" t="s">
-        <v>70</v>
-      </c>
-      <c r="C14" t="s">
-        <v>68</v>
-      </c>
-      <c r="D14" t="s">
-        <v>112</v>
-      </c>
-      <c r="E14" t="s">
-        <v>9</v>
-      </c>
-      <c r="F14" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>20330051920346</v>
-      </c>
-      <c r="B15" t="s">
-        <v>70</v>
-      </c>
-      <c r="C15" t="s">
-        <v>91</v>
-      </c>
-      <c r="D15" t="s">
-        <v>113</v>
-      </c>
-      <c r="E15" t="s">
-        <v>9</v>
-      </c>
-      <c r="F15" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>21330051920123</v>
-      </c>
-      <c r="B16" t="s">
-        <v>71</v>
-      </c>
-      <c r="C16" t="s">
-        <v>92</v>
-      </c>
-      <c r="D16" t="s">
-        <v>114</v>
-      </c>
-      <c r="E16" t="s">
-        <v>9</v>
-      </c>
-      <c r="F16" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>21330051920125</v>
-      </c>
-      <c r="B17" t="s">
-        <v>72</v>
-      </c>
-      <c r="C17" t="s">
-        <v>67</v>
-      </c>
-      <c r="D17" t="s">
-        <v>115</v>
-      </c>
-      <c r="E17" t="s">
-        <v>9</v>
-      </c>
-      <c r="F17" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>21330051920126</v>
-      </c>
-      <c r="B18" t="s">
-        <v>73</v>
-      </c>
-      <c r="C18" t="s">
-        <v>93</v>
-      </c>
-      <c r="D18" t="s">
-        <v>116</v>
-      </c>
-      <c r="E18" t="s">
-        <v>9</v>
-      </c>
-      <c r="F18" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>21330051920127</v>
-      </c>
-      <c r="B19" t="s">
-        <v>74</v>
-      </c>
-      <c r="C19" t="s">
-        <v>94</v>
-      </c>
-      <c r="D19" t="s">
-        <v>117</v>
-      </c>
-      <c r="E19" t="s">
-        <v>9</v>
-      </c>
-      <c r="F19" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>21330051920129</v>
-      </c>
-      <c r="C20" t="s">
-        <v>95</v>
-      </c>
-      <c r="D20" t="s">
-        <v>118</v>
-      </c>
-      <c r="E20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F20" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>21330051920130</v>
-      </c>
-      <c r="B21" t="s">
-        <v>75</v>
-      </c>
-      <c r="C21" t="s">
-        <v>96</v>
-      </c>
-      <c r="D21" t="s">
-        <v>119</v>
-      </c>
-      <c r="E21" t="s">
-        <v>9</v>
-      </c>
-      <c r="F21" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>21330051920131</v>
-      </c>
-      <c r="B22" t="s">
-        <v>76</v>
-      </c>
-      <c r="C22" t="s">
-        <v>97</v>
-      </c>
-      <c r="D22" t="s">
-        <v>120</v>
-      </c>
-      <c r="E22" t="s">
-        <v>9</v>
-      </c>
-      <c r="F22" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>18330051920377</v>
-      </c>
-      <c r="B23" t="s">
-        <v>77</v>
-      </c>
-      <c r="C23" t="s">
-        <v>98</v>
-      </c>
-      <c r="D23" t="s">
-        <v>121</v>
-      </c>
-      <c r="E23" t="s">
-        <v>9</v>
-      </c>
-      <c r="F23" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>21330051920132</v>
-      </c>
-      <c r="B24" t="s">
-        <v>78</v>
-      </c>
-      <c r="C24" t="s">
-        <v>99</v>
-      </c>
-      <c r="D24" t="s">
-        <v>122</v>
-      </c>
-      <c r="E24" t="s">
-        <v>9</v>
-      </c>
-      <c r="F24" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>20330051920152</v>
-      </c>
-      <c r="B25" t="s">
-        <v>79</v>
-      </c>
-      <c r="C25" t="s">
-        <v>62</v>
-      </c>
-      <c r="D25" t="s">
-        <v>123</v>
-      </c>
-      <c r="E25" t="s">
-        <v>9</v>
-      </c>
-      <c r="F25" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26">
-        <v>21330051920133</v>
-      </c>
-      <c r="B26" t="s">
-        <v>80</v>
-      </c>
-      <c r="C26" t="s">
-        <v>100</v>
-      </c>
-      <c r="D26" t="s">
-        <v>124</v>
-      </c>
-      <c r="E26" t="s">
-        <v>9</v>
-      </c>
-      <c r="F26" t="s">
         <v>50</v>
       </c>
     </row>
@@ -5751,16 +5277,16 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>21330051920111</v>
+        <v>20330051920346</v>
       </c>
       <c r="B2" t="s">
         <v>61</v>
       </c>
       <c r="C2" t="s">
-        <v>81</v>
+        <v>62</v>
       </c>
       <c r="D2" t="s">
-        <v>101</v>
+        <v>63</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -5768,223 +5294,223 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>21330051920112</v>
+        <v>21330051920111</v>
       </c>
       <c r="B3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D3" t="s">
         <v>102</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>21330051920113</v>
+        <v>21330051920112</v>
       </c>
       <c r="B4" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C4" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="D4" t="s">
         <v>103</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>21330051920114</v>
+        <v>21330051920113</v>
       </c>
       <c r="B5" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C5" t="s">
-        <v>83</v>
+        <v>61</v>
       </c>
       <c r="D5" t="s">
         <v>104</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>21330051920116</v>
+        <v>21330051920114</v>
       </c>
       <c r="B6" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D6" t="s">
         <v>105</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>21330051920117</v>
+        <v>21330051920116</v>
       </c>
       <c r="B7" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D7" t="s">
         <v>106</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>21330051920118</v>
+        <v>21330051920117</v>
       </c>
       <c r="B8" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D8" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>21330051920119</v>
+        <v>21330051920118</v>
       </c>
       <c r="B9" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D9" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>20330051920266</v>
+        <v>21330051920119</v>
       </c>
       <c r="B10" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D10" t="s">
         <v>108</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>21330051920120</v>
+        <v>20330051920266</v>
       </c>
       <c r="B11" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D11" t="s">
         <v>109</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>21330051920121</v>
+        <v>21330051920120</v>
       </c>
       <c r="B12" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C12" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="D12" t="s">
         <v>110</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>21330051920391</v>
+        <v>21330051920121</v>
       </c>
       <c r="B13" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C13" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="D13" t="s">
         <v>111</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>21330051920122</v>
+        <v>21330051920391</v>
       </c>
       <c r="B14" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C14" t="s">
-        <v>68</v>
+        <v>92</v>
       </c>
       <c r="D14" t="s">
         <v>112</v>
       </c>
       <c r="E14">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>20330051920346</v>
+        <v>21330051920122</v>
       </c>
       <c r="B15" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="C15" t="s">
-        <v>91</v>
+        <v>71</v>
       </c>
       <c r="D15" t="s">
         <v>113</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -5992,16 +5518,16 @@
         <v>21330051920123</v>
       </c>
       <c r="B16" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C16" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D16" t="s">
         <v>114</v>
       </c>
       <c r="E16">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -6009,16 +5535,16 @@
         <v>21330051920125</v>
       </c>
       <c r="B17" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C17" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D17" t="s">
         <v>115</v>
       </c>
       <c r="E17">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -6026,16 +5552,16 @@
         <v>21330051920126</v>
       </c>
       <c r="B18" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C18" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D18" t="s">
         <v>116</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -6043,16 +5569,16 @@
         <v>21330051920127</v>
       </c>
       <c r="B19" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C19" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D19" t="s">
         <v>117</v>
       </c>
       <c r="E19">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -6060,13 +5586,13 @@
         <v>21330051920129</v>
       </c>
       <c r="C20" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D20" t="s">
         <v>118</v>
       </c>
       <c r="E20">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -6074,16 +5600,16 @@
         <v>21330051920130</v>
       </c>
       <c r="B21" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C21" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D21" t="s">
         <v>119</v>
       </c>
       <c r="E21">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -6091,16 +5617,16 @@
         <v>21330051920131</v>
       </c>
       <c r="B22" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C22" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D22" t="s">
         <v>120</v>
       </c>
       <c r="E22">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -6108,16 +5634,16 @@
         <v>18330051920377</v>
       </c>
       <c r="B23" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C23" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D23" t="s">
         <v>121</v>
       </c>
       <c r="E23">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -6125,16 +5651,16 @@
         <v>21330051920132</v>
       </c>
       <c r="B24" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C24" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D24" t="s">
         <v>122</v>
       </c>
       <c r="E24">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -6142,16 +5668,16 @@
         <v>20330051920152</v>
       </c>
       <c r="B25" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C25" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D25" t="s">
         <v>123</v>
       </c>
       <c r="E25">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -6159,16 +5685,16 @@
         <v>21330051920133</v>
       </c>
       <c r="B26" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C26" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D26" t="s">
         <v>124</v>
       </c>
       <c r="E26">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -6178,7 +5704,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6210,45 +5736,45 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920121</v>
+        <v>21330051920111</v>
       </c>
       <c r="B2" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D2" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920121</v>
+        <v>21330051920111</v>
       </c>
       <c r="B3" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D3" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -6259,13 +5785,13 @@
         <v>21330051920122</v>
       </c>
       <c r="B4" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="C4" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="D4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
@@ -6274,7 +5800,7 @@
         <v>50</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -6282,13 +5808,13 @@
         <v>21330051920122</v>
       </c>
       <c r="B5" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="C5" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="D5" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E5" t="s">
         <v>11</v>
@@ -6305,10 +5831,10 @@
         <v>18330051920377</v>
       </c>
       <c r="B6" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D6" t="s">
         <v>121</v>
@@ -6320,7 +5846,7 @@
         <v>50</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -6328,10 +5854,10 @@
         <v>18330051920377</v>
       </c>
       <c r="B7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D7" t="s">
         <v>121</v>
@@ -6351,10 +5877,10 @@
         <v>20330051920152</v>
       </c>
       <c r="B8" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C8" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D8" t="s">
         <v>123</v>
@@ -6374,10 +5900,10 @@
         <v>20330051920152</v>
       </c>
       <c r="B9" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C9" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D9" t="s">
         <v>123</v>
@@ -6389,7 +5915,7 @@
         <v>50</v>
       </c>
       <c r="G9">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -6397,13 +5923,13 @@
         <v>21330051920114</v>
       </c>
       <c r="B10" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C10" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D10" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E10" t="s">
         <v>9</v>
@@ -6412,165 +5938,30 @@
         <v>50</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920116</v>
+        <v>21330051920121</v>
       </c>
       <c r="B11" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="C11" t="s">
         <v>84</v>
       </c>
       <c r="D11" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="E11" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G11">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>21330051920118</v>
-      </c>
-      <c r="B12" t="s">
-        <v>67</v>
-      </c>
-      <c r="C12" t="s">
-        <v>86</v>
-      </c>
-      <c r="D12" t="s">
-        <v>102</v>
-      </c>
-      <c r="E12" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" t="s">
-        <v>50</v>
-      </c>
-      <c r="G12">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>20330051920266</v>
-      </c>
-      <c r="B13" t="s">
-        <v>68</v>
-      </c>
-      <c r="C13" t="s">
-        <v>88</v>
-      </c>
-      <c r="D13" t="s">
-        <v>108</v>
-      </c>
-      <c r="E13" t="s">
-        <v>9</v>
-      </c>
-      <c r="F13" t="s">
-        <v>50</v>
-      </c>
-      <c r="G13">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>21330051920123</v>
-      </c>
-      <c r="B14" t="s">
-        <v>71</v>
-      </c>
-      <c r="C14" t="s">
-        <v>92</v>
-      </c>
-      <c r="D14" t="s">
-        <v>114</v>
-      </c>
-      <c r="E14" t="s">
-        <v>9</v>
-      </c>
-      <c r="F14" t="s">
-        <v>50</v>
-      </c>
-      <c r="G14">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>21330051920129</v>
-      </c>
-      <c r="C15" t="s">
-        <v>95</v>
-      </c>
-      <c r="D15" t="s">
-        <v>118</v>
-      </c>
-      <c r="E15" t="s">
-        <v>9</v>
-      </c>
-      <c r="F15" t="s">
-        <v>50</v>
-      </c>
-      <c r="G15">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>21330051920131</v>
-      </c>
-      <c r="B16" t="s">
-        <v>76</v>
-      </c>
-      <c r="C16" t="s">
-        <v>97</v>
-      </c>
-      <c r="D16" t="s">
-        <v>120</v>
-      </c>
-      <c r="E16" t="s">
-        <v>9</v>
-      </c>
-      <c r="F16" t="s">
-        <v>50</v>
-      </c>
-      <c r="G16">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>21330051920132</v>
-      </c>
-      <c r="B17" t="s">
-        <v>78</v>
-      </c>
-      <c r="C17" t="s">
-        <v>99</v>
-      </c>
-      <c r="D17" t="s">
-        <v>122</v>
-      </c>
-      <c r="E17" t="s">
-        <v>9</v>
-      </c>
-      <c r="F17" t="s">
-        <v>50</v>
-      </c>
-      <c r="G17">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/4APV - Estadisticos 20222.xlsx
+++ b/grupos/4APV - Estadisticos 20222.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="125">
   <si>
     <t>Materia</t>
   </si>
@@ -204,163 +204,163 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>BARRAGAN</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>CERVANTES</t>
+  </si>
+  <si>
+    <t>CERON</t>
+  </si>
+  <si>
+    <t>DOMINGUEZ</t>
+  </si>
+  <si>
+    <t>ENCARNACION</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
+    <t>LIBRADO</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MARIN</t>
+  </si>
+  <si>
+    <t>MONT</t>
+  </si>
+  <si>
+    <t>QUERO</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>TZOMPAXTLE</t>
+  </si>
+  <si>
+    <t>MARCELINO</t>
+  </si>
+  <si>
+    <t>MONTALVO</t>
+  </si>
+  <si>
+    <t>VILLA</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>NIEVES</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>CAPORAL</t>
+  </si>
+  <si>
     <t>SARMIENTO</t>
   </si>
   <si>
+    <t>CORONADO</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>BRAVO</t>
+  </si>
+  <si>
+    <t>OCHOA</t>
+  </si>
+  <si>
+    <t>SERRANO</t>
+  </si>
+  <si>
+    <t>VILLEGAS</t>
+  </si>
+  <si>
+    <t>TLAXCALTECA</t>
+  </si>
+  <si>
+    <t>ARELLANO</t>
+  </si>
+  <si>
+    <t>MONTIEL</t>
+  </si>
+  <si>
+    <t>KAREN ITZEL</t>
+  </si>
+  <si>
+    <t>DIEGO</t>
+  </si>
+  <si>
+    <t>SAMANTHA MIA</t>
+  </si>
+  <si>
+    <t>MARIA JOSE</t>
+  </si>
+  <si>
+    <t>MARILYN</t>
+  </si>
+  <si>
+    <t>DIANA IRAIS</t>
+  </si>
+  <si>
+    <t>GAEL</t>
+  </si>
+  <si>
+    <t>JOSE LUIS</t>
+  </si>
+  <si>
+    <t>NATALIE</t>
+  </si>
+  <si>
+    <t>CRISTIAN FERMIN</t>
+  </si>
+  <si>
+    <t>LOGAN FRANCISCO</t>
+  </si>
+  <si>
+    <t>CLAUDIA</t>
+  </si>
+  <si>
     <t>JESUS</t>
-  </si>
-  <si>
-    <t>BARRAGAN</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>CERVANTES</t>
-  </si>
-  <si>
-    <t>CERON</t>
-  </si>
-  <si>
-    <t>DOMINGUEZ</t>
-  </si>
-  <si>
-    <t>ENCARNACION</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>LIBRADO</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MARIN</t>
-  </si>
-  <si>
-    <t>MONT</t>
-  </si>
-  <si>
-    <t>QUERO</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>TZOMPAXTLE</t>
-  </si>
-  <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
-    <t>MONTALVO</t>
-  </si>
-  <si>
-    <t>VILLA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>NIEVES</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>CAPORAL</t>
-  </si>
-  <si>
-    <t>CORONADO</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>BRAVO</t>
-  </si>
-  <si>
-    <t>OCHOA</t>
-  </si>
-  <si>
-    <t>SERRANO</t>
-  </si>
-  <si>
-    <t>VILLEGAS</t>
-  </si>
-  <si>
-    <t>TLAXCALTECA</t>
-  </si>
-  <si>
-    <t>ARELLANO</t>
-  </si>
-  <si>
-    <t>MONTIEL</t>
-  </si>
-  <si>
-    <t>KAREN ITZEL</t>
-  </si>
-  <si>
-    <t>DIEGO</t>
-  </si>
-  <si>
-    <t>SAMANTHA MIA</t>
-  </si>
-  <si>
-    <t>MARIA JOSE</t>
-  </si>
-  <si>
-    <t>MARILYN</t>
-  </si>
-  <si>
-    <t>DIANA IRAIS</t>
-  </si>
-  <si>
-    <t>GAEL</t>
-  </si>
-  <si>
-    <t>JOSE LUIS</t>
-  </si>
-  <si>
-    <t>NATALIE</t>
-  </si>
-  <si>
-    <t>CRISTIAN FERMIN</t>
-  </si>
-  <si>
-    <t>LOGAN FRANCISCO</t>
-  </si>
-  <si>
-    <t>CLAUDIA</t>
   </si>
   <si>
     <t>LIZBETH</t>
@@ -2153,7 +2153,7 @@
         <v>5</v>
       </c>
       <c r="F18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H18">
         <v>0</v>
@@ -2207,7 +2207,7 @@
         <v>5</v>
       </c>
       <c r="AA18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC18">
         <v>5</v>
@@ -4980,22 +4980,22 @@
         <v>9</v>
       </c>
       <c r="E2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F2">
         <v>36</v>
       </c>
       <c r="G2">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="H2">
         <v>6.1</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -5197,7 +5197,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5222,26 +5222,6 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>20330051920346</v>
-      </c>
-      <c r="B2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C2" t="s">
-        <v>62</v>
-      </c>
-      <c r="D2" t="s">
-        <v>63</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" t="s">
-        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -5277,30 +5257,30 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>20330051920346</v>
+        <v>21330051920111</v>
       </c>
       <c r="B2" t="s">
         <v>61</v>
       </c>
       <c r="C2" t="s">
-        <v>62</v>
+        <v>81</v>
       </c>
       <c r="D2" t="s">
-        <v>63</v>
+        <v>101</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>21330051920111</v>
+        <v>21330051920112</v>
       </c>
       <c r="B3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D3" t="s">
         <v>102</v>
@@ -5311,13 +5291,13 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>21330051920112</v>
+        <v>21330051920113</v>
       </c>
       <c r="B4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C4" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="D4" t="s">
         <v>103</v>
@@ -5328,13 +5308,13 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>21330051920113</v>
+        <v>21330051920114</v>
       </c>
       <c r="B5" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C5" t="s">
-        <v>61</v>
+        <v>83</v>
       </c>
       <c r="D5" t="s">
         <v>104</v>
@@ -5345,13 +5325,13 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>21330051920114</v>
+        <v>21330051920116</v>
       </c>
       <c r="B6" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D6" t="s">
         <v>105</v>
@@ -5362,13 +5342,13 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>21330051920116</v>
+        <v>21330051920117</v>
       </c>
       <c r="B7" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D7" t="s">
         <v>106</v>
@@ -5379,16 +5359,16 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>21330051920117</v>
+        <v>21330051920118</v>
       </c>
       <c r="B8" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C8" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D8" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -5396,16 +5376,16 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>21330051920118</v>
+        <v>21330051920119</v>
       </c>
       <c r="B9" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D9" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -5413,13 +5393,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>21330051920119</v>
+        <v>20330051920266</v>
       </c>
       <c r="B10" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D10" t="s">
         <v>108</v>
@@ -5430,13 +5410,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>20330051920266</v>
+        <v>21330051920120</v>
       </c>
       <c r="B11" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D11" t="s">
         <v>109</v>
@@ -5447,13 +5427,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>21330051920120</v>
+        <v>21330051920121</v>
       </c>
       <c r="B12" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C12" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="D12" t="s">
         <v>110</v>
@@ -5464,13 +5444,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>21330051920121</v>
+        <v>21330051920391</v>
       </c>
       <c r="B13" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C13" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="D13" t="s">
         <v>111</v>
@@ -5481,13 +5461,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>21330051920391</v>
+        <v>21330051920122</v>
       </c>
       <c r="B14" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C14" t="s">
-        <v>92</v>
+        <v>68</v>
       </c>
       <c r="D14" t="s">
         <v>112</v>
@@ -5498,13 +5478,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>21330051920122</v>
+        <v>20330051920346</v>
       </c>
       <c r="B15" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="C15" t="s">
-        <v>71</v>
+        <v>91</v>
       </c>
       <c r="D15" t="s">
         <v>113</v>
@@ -5518,10 +5498,10 @@
         <v>21330051920123</v>
       </c>
       <c r="B16" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D16" t="s">
         <v>114</v>
@@ -5535,10 +5515,10 @@
         <v>21330051920125</v>
       </c>
       <c r="B17" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C17" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D17" t="s">
         <v>115</v>
@@ -5552,10 +5532,10 @@
         <v>21330051920126</v>
       </c>
       <c r="B18" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C18" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D18" t="s">
         <v>116</v>
@@ -5569,10 +5549,10 @@
         <v>21330051920127</v>
       </c>
       <c r="B19" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C19" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D19" t="s">
         <v>117</v>
@@ -5586,7 +5566,7 @@
         <v>21330051920129</v>
       </c>
       <c r="C20" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D20" t="s">
         <v>118</v>
@@ -5600,10 +5580,10 @@
         <v>21330051920130</v>
       </c>
       <c r="B21" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C21" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D21" t="s">
         <v>119</v>
@@ -5617,10 +5597,10 @@
         <v>21330051920131</v>
       </c>
       <c r="B22" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C22" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D22" t="s">
         <v>120</v>
@@ -5634,10 +5614,10 @@
         <v>18330051920377</v>
       </c>
       <c r="B23" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C23" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D23" t="s">
         <v>121</v>
@@ -5651,10 +5631,10 @@
         <v>21330051920132</v>
       </c>
       <c r="B24" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C24" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D24" t="s">
         <v>122</v>
@@ -5668,10 +5648,10 @@
         <v>20330051920152</v>
       </c>
       <c r="B25" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C25" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D25" t="s">
         <v>123</v>
@@ -5685,10 +5665,10 @@
         <v>21330051920133</v>
       </c>
       <c r="B26" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C26" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D26" t="s">
         <v>124</v>
@@ -5739,13 +5719,13 @@
         <v>21330051920111</v>
       </c>
       <c r="B2" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E2" t="s">
         <v>10</v>
@@ -5762,13 +5742,13 @@
         <v>21330051920111</v>
       </c>
       <c r="B3" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E3" t="s">
         <v>11</v>
@@ -5785,13 +5765,13 @@
         <v>21330051920122</v>
       </c>
       <c r="B4" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="C4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
@@ -5808,13 +5788,13 @@
         <v>21330051920122</v>
       </c>
       <c r="B5" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="C5" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E5" t="s">
         <v>11</v>
@@ -5831,10 +5811,10 @@
         <v>18330051920377</v>
       </c>
       <c r="B6" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D6" t="s">
         <v>121</v>
@@ -5854,10 +5834,10 @@
         <v>18330051920377</v>
       </c>
       <c r="B7" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D7" t="s">
         <v>121</v>
@@ -5877,10 +5857,10 @@
         <v>20330051920152</v>
       </c>
       <c r="B8" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C8" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D8" t="s">
         <v>123</v>
@@ -5900,10 +5880,10 @@
         <v>20330051920152</v>
       </c>
       <c r="B9" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C9" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D9" t="s">
         <v>123</v>
@@ -5923,13 +5903,13 @@
         <v>21330051920114</v>
       </c>
       <c r="B10" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C10" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D10" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E10" t="s">
         <v>9</v>
@@ -5946,13 +5926,13 @@
         <v>21330051920121</v>
       </c>
       <c r="B11" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C11" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>

--- a/grupos/4APV - Estadisticos 20222.xlsx
+++ b/grupos/4APV - Estadisticos 20222.xlsx
@@ -11,15 +11,14 @@
     <sheet name="Asistencias" sheetId="2" r:id="rId2"/>
     <sheet name="Totales" sheetId="3" r:id="rId3"/>
     <sheet name="Blancos" sheetId="4" r:id="rId4"/>
-    <sheet name="Totales Blanco" sheetId="5" r:id="rId5"/>
-    <sheet name="Rescatables" sheetId="6" r:id="rId6"/>
+    <sheet name="Rescatables" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="73">
   <si>
     <t>Materia</t>
   </si>
@@ -183,12 +182,12 @@
     <t>Rodriguez Roman Marisol</t>
   </si>
   <si>
+    <t>Muñoz Rivadeneyra Salvador</t>
+  </si>
+  <si>
     <t>Acevedo Rendón Ismael Arturo</t>
   </si>
   <si>
-    <t>Muñoz Rivadeneyra Salvador</t>
-  </si>
-  <si>
     <t>De Jesús Orduña Sofía del Pilar</t>
   </si>
   <si>
@@ -207,199 +206,46 @@
     <t>BARRAGAN</t>
   </si>
   <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>CERON</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
     <t>CASTRO</t>
   </si>
   <si>
-    <t>CERVANTES</t>
-  </si>
-  <si>
-    <t>CERON</t>
-  </si>
-  <si>
-    <t>DOMINGUEZ</t>
-  </si>
-  <si>
-    <t>ENCARNACION</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>LIBRADO</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MARIN</t>
-  </si>
-  <si>
-    <t>MONT</t>
-  </si>
-  <si>
-    <t>QUERO</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
     <t>TZOMPAXTLE</t>
   </si>
   <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
-    <t>MONTALVO</t>
-  </si>
-  <si>
     <t>VILLA</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>NIEVES</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>CAPORAL</t>
-  </si>
-  <si>
-    <t>SARMIENTO</t>
-  </si>
-  <si>
-    <t>CORONADO</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>BRAVO</t>
-  </si>
-  <si>
-    <t>OCHOA</t>
-  </si>
-  <si>
-    <t>SERRANO</t>
-  </si>
-  <si>
-    <t>VILLEGAS</t>
-  </si>
-  <si>
-    <t>TLAXCALTECA</t>
-  </si>
-  <si>
-    <t>ARELLANO</t>
-  </si>
-  <si>
-    <t>MONTIEL</t>
-  </si>
-  <si>
     <t>KAREN ITZEL</t>
   </si>
   <si>
+    <t>MARIA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>MARIA JOSE</t>
+  </si>
+  <si>
     <t>DIEGO</t>
-  </si>
-  <si>
-    <t>SAMANTHA MIA</t>
-  </si>
-  <si>
-    <t>MARIA JOSE</t>
-  </si>
-  <si>
-    <t>MARILYN</t>
-  </si>
-  <si>
-    <t>DIANA IRAIS</t>
-  </si>
-  <si>
-    <t>GAEL</t>
-  </si>
-  <si>
-    <t>JOSE LUIS</t>
-  </si>
-  <si>
-    <t>NATALIE</t>
-  </si>
-  <si>
-    <t>CRISTIAN FERMIN</t>
-  </si>
-  <si>
-    <t>LOGAN FRANCISCO</t>
-  </si>
-  <si>
-    <t>CLAUDIA</t>
-  </si>
-  <si>
-    <t>JESUS</t>
-  </si>
-  <si>
-    <t>LIZBETH</t>
-  </si>
-  <si>
-    <t>ZABDIEL</t>
-  </si>
-  <si>
-    <t>ALEJANDRO</t>
-  </si>
-  <si>
-    <t>PAUL ADRIAN</t>
-  </si>
-  <si>
-    <t>DANIEL OCTAVIO</t>
-  </si>
-  <si>
-    <t>EDWIN YAMIL</t>
-  </si>
-  <si>
-    <t>FATIMA</t>
-  </si>
-  <si>
-    <t>MARIANA</t>
-  </si>
-  <si>
-    <t>GABRIELA DENISSE</t>
-  </si>
-  <si>
-    <t>MARIA DEL CARMEN</t>
-  </si>
-  <si>
-    <t>CESAR DANIEL</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0\%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -452,11 +298,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -916,22 +763,22 @@
         <v>9</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J4">
         <v>-1</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M4">
         <v>-1</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O4">
         <v>-1</v>
@@ -973,7 +820,7 @@
         <v>9</v>
       </c>
       <c r="AB4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC4">
         <v>9</v>
@@ -1005,22 +852,22 @@
         <v>5</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J5">
         <v>-1</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M5">
         <v>-1</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O5">
         <v>-1</v>
@@ -1053,10 +900,10 @@
         <v>6</v>
       </c>
       <c r="Y5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA5">
         <v>6</v>
@@ -1094,22 +941,22 @@
         <v>5</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J6">
         <v>-1</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M6">
         <v>-1</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O6">
         <v>-1</v>
@@ -1136,7 +983,7 @@
         <v>-1</v>
       </c>
       <c r="W6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X6">
         <v>5</v>
@@ -1183,22 +1030,22 @@
         <v>8</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J7">
         <v>-1</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M7">
         <v>-1</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O7">
         <v>-1</v>
@@ -1225,13 +1072,13 @@
         <v>-1</v>
       </c>
       <c r="W7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X7">
         <v>6</v>
       </c>
       <c r="Y7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z7">
         <v>9</v>
@@ -1240,7 +1087,7 @@
         <v>5</v>
       </c>
       <c r="AB7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC7">
         <v>8</v>
@@ -1272,22 +1119,22 @@
         <v>6</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J8">
         <v>-1</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M8">
         <v>-1</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O8">
         <v>-1</v>
@@ -1320,10 +1167,10 @@
         <v>5</v>
       </c>
       <c r="Y8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA8">
         <v>5</v>
@@ -1361,22 +1208,22 @@
         <v>10</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J9">
         <v>-1</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M9">
         <v>-1</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O9">
         <v>-1</v>
@@ -1403,7 +1250,7 @@
         <v>-1</v>
       </c>
       <c r="W9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X9">
         <v>10</v>
@@ -1418,7 +1265,7 @@
         <v>10</v>
       </c>
       <c r="AB9">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AC9">
         <v>10</v>
@@ -1450,22 +1297,22 @@
         <v>7</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J10">
         <v>-1</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M10">
         <v>-1</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O10">
         <v>-1</v>
@@ -1498,7 +1345,7 @@
         <v>7</v>
       </c>
       <c r="Y10">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z10">
         <v>5</v>
@@ -1507,7 +1354,7 @@
         <v>5</v>
       </c>
       <c r="AB10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC10">
         <v>7</v>
@@ -1539,22 +1386,22 @@
         <v>8</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J11">
         <v>-1</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M11">
         <v>-1</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O11">
         <v>-1</v>
@@ -1596,7 +1443,7 @@
         <v>9</v>
       </c>
       <c r="AB11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC11">
         <v>8</v>
@@ -1628,22 +1475,22 @@
         <v>6</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J12">
         <v>-1</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M12">
         <v>-1</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O12">
         <v>-1</v>
@@ -1679,13 +1526,13 @@
         <v>5</v>
       </c>
       <c r="Z12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA12">
         <v>5</v>
       </c>
       <c r="AB12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC12">
         <v>6</v>
@@ -1717,22 +1564,22 @@
         <v>8</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J13">
         <v>-1</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M13">
         <v>-1</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O13">
         <v>-1</v>
@@ -1759,13 +1606,13 @@
         <v>-1</v>
       </c>
       <c r="W13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X13">
         <v>8</v>
       </c>
       <c r="Y13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z13">
         <v>9</v>
@@ -1774,7 +1621,7 @@
         <v>8</v>
       </c>
       <c r="AB13">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC13">
         <v>8</v>
@@ -1806,22 +1653,22 @@
         <v>6</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J14">
         <v>-1</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M14">
         <v>-1</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O14">
         <v>-1</v>
@@ -1895,22 +1742,22 @@
         <v>9</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J15">
         <v>-1</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M15">
         <v>-1</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O15">
         <v>-1</v>
@@ -1937,7 +1784,7 @@
         <v>-1</v>
       </c>
       <c r="W15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X15">
         <v>6</v>
@@ -1952,7 +1799,7 @@
         <v>9</v>
       </c>
       <c r="AB15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC15">
         <v>9</v>
@@ -1984,22 +1831,22 @@
         <v>5</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J16">
         <v>-1</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M16">
         <v>-1</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O16">
         <v>-1</v>
@@ -2026,16 +1873,16 @@
         <v>-1</v>
       </c>
       <c r="W16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X16">
         <v>5</v>
       </c>
       <c r="Y16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA16">
         <v>5</v>
@@ -2073,22 +1920,22 @@
         <v>5</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J17">
         <v>-1</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M17">
         <v>-1</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O17">
         <v>-1</v>
@@ -2121,16 +1968,16 @@
         <v>7</v>
       </c>
       <c r="Y17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA17">
         <v>5</v>
       </c>
       <c r="AB17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC17">
         <v>5</v>
@@ -2159,16 +2006,16 @@
         <v>0</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J18">
         <v>-1</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M18">
         <v>-1</v>
@@ -2239,22 +2086,22 @@
         <v>7</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J19">
         <v>-1</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M19">
         <v>-1</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O19">
         <v>-1</v>
@@ -2281,22 +2128,22 @@
         <v>-1</v>
       </c>
       <c r="W19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X19">
         <v>7</v>
       </c>
       <c r="Y19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA19">
         <v>7</v>
       </c>
       <c r="AB19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC19">
         <v>7</v>
@@ -2328,22 +2175,22 @@
         <v>5</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J20">
         <v>-1</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M20">
         <v>-1</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O20">
         <v>-1</v>
@@ -2417,22 +2264,22 @@
         <v>5</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J21">
         <v>-1</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M21">
         <v>-1</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O21">
         <v>-1</v>
@@ -2468,7 +2315,7 @@
         <v>7</v>
       </c>
       <c r="Z21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA21">
         <v>5</v>
@@ -2506,22 +2353,22 @@
         <v>5</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J22">
         <v>-1</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M22">
         <v>-1</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O22">
         <v>-1</v>
@@ -2595,22 +2442,22 @@
         <v>5</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J23">
         <v>-1</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M23">
         <v>-1</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O23">
         <v>-1</v>
@@ -2637,13 +2484,13 @@
         <v>-1</v>
       </c>
       <c r="W23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X23">
         <v>7</v>
       </c>
       <c r="Y23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z23">
         <v>5</v>
@@ -2652,7 +2499,7 @@
         <v>5</v>
       </c>
       <c r="AB23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC23">
         <v>5</v>
@@ -2684,22 +2531,22 @@
         <v>7</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J24">
         <v>-1</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M24">
         <v>-1</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O24">
         <v>-1</v>
@@ -2732,16 +2579,16 @@
         <v>10</v>
       </c>
       <c r="Y24">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA24">
         <v>7</v>
       </c>
       <c r="AB24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC24">
         <v>7</v>
@@ -2773,22 +2620,22 @@
         <v>5</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J25">
         <v>-1</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M25">
         <v>-1</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O25">
         <v>-1</v>
@@ -2830,7 +2677,7 @@
         <v>5</v>
       </c>
       <c r="AB25">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC25">
         <v>5</v>
@@ -2862,22 +2709,22 @@
         <v>8</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J26">
         <v>-1</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M26">
         <v>-1</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O26">
         <v>-1</v>
@@ -2919,7 +2766,7 @@
         <v>7</v>
       </c>
       <c r="AB26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC26">
         <v>8</v>
@@ -2951,22 +2798,22 @@
         <v>7</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J27">
         <v>-1</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M27">
         <v>-1</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O27">
         <v>-1</v>
@@ -2999,10 +2846,10 @@
         <v>7</v>
       </c>
       <c r="Y27">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA27">
         <v>5</v>
@@ -3040,22 +2887,22 @@
         <v>6</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J28">
         <v>-1</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M28">
         <v>-1</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O28">
         <v>-1</v>
@@ -3251,22 +3098,22 @@
         <v>120</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J4">
         <v>0</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M4">
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O4">
         <v>0</v>
@@ -3319,22 +3166,22 @@
         <v>93.3</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="J5">
         <v>0</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>86.7</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>85.7</v>
       </c>
       <c r="M5">
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="O5">
         <v>0</v>
@@ -3393,16 +3240,16 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>73.3</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>42.9</v>
       </c>
       <c r="M6">
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="O6">
         <v>0</v>
@@ -3455,22 +3302,22 @@
         <v>93.3</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="J7">
         <v>0</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>85.7</v>
       </c>
       <c r="M7">
         <v>0</v>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="O7">
         <v>0</v>
@@ -3529,16 +3376,16 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="M8">
         <v>0</v>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="O8">
         <v>0</v>
@@ -3591,22 +3438,22 @@
         <v>120</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J9">
         <v>0</v>
       </c>
       <c r="K9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M9">
         <v>0</v>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="O9">
         <v>0</v>
@@ -3659,22 +3506,22 @@
         <v>120</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J10">
         <v>0</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>73.3</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="M10">
         <v>0</v>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="O10">
         <v>0</v>
@@ -3727,22 +3574,22 @@
         <v>120</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J11">
         <v>0</v>
       </c>
       <c r="K11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M11">
         <v>0</v>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O11">
         <v>0</v>
@@ -3795,22 +3642,22 @@
         <v>93.3</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J12">
         <v>0</v>
       </c>
       <c r="K12">
-        <v>0</v>
+        <v>86.7</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="M12">
         <v>0</v>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="O12">
         <v>0</v>
@@ -3863,22 +3710,22 @@
         <v>120</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J13">
         <v>0</v>
       </c>
       <c r="K13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M13">
         <v>0</v>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="O13">
         <v>0</v>
@@ -3931,22 +3778,22 @@
         <v>93.3</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J14">
         <v>0</v>
       </c>
       <c r="K14">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="L14">
-        <v>0</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="M14">
         <v>0</v>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="O14">
         <v>0</v>
@@ -3999,22 +3846,22 @@
         <v>120</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J15">
         <v>0</v>
       </c>
       <c r="K15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="M15">
         <v>0</v>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O15">
         <v>0</v>
@@ -4067,22 +3914,22 @@
         <v>93.3</v>
       </c>
       <c r="I16">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="J16">
         <v>0</v>
       </c>
       <c r="K16">
-        <v>0</v>
+        <v>86.7</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="M16">
         <v>0</v>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="O16">
         <v>0</v>
@@ -4135,22 +3982,22 @@
         <v>120</v>
       </c>
       <c r="I17">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="J17">
         <v>0</v>
       </c>
       <c r="K17">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="L17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M17">
         <v>0</v>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="O17">
         <v>0</v>
@@ -4262,22 +4109,22 @@
         <v>120</v>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="J19">
         <v>0</v>
       </c>
       <c r="K19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L19">
-        <v>0</v>
+        <v>94.3</v>
       </c>
       <c r="M19">
         <v>0</v>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="O19">
         <v>0</v>
@@ -4330,22 +4177,22 @@
         <v>26.7</v>
       </c>
       <c r="I20">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J20">
         <v>0</v>
       </c>
       <c r="K20">
-        <v>0</v>
+        <v>86.7</v>
       </c>
       <c r="L20">
-        <v>0</v>
+        <v>54.3</v>
       </c>
       <c r="M20">
         <v>0</v>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="O20">
         <v>0</v>
@@ -4398,22 +4245,22 @@
         <v>33.3</v>
       </c>
       <c r="I21">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="J21">
         <v>0</v>
       </c>
       <c r="K21">
-        <v>0</v>
+        <v>73.3</v>
       </c>
       <c r="L21">
-        <v>0</v>
+        <v>57.1</v>
       </c>
       <c r="M21">
         <v>0</v>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="O21">
         <v>0</v>
@@ -4466,22 +4313,22 @@
         <v>33.3</v>
       </c>
       <c r="I22">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="J22">
         <v>0</v>
       </c>
       <c r="K22">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="L22">
-        <v>0</v>
+        <v>65.7</v>
       </c>
       <c r="M22">
         <v>0</v>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="O22">
         <v>0</v>
@@ -4534,22 +4381,22 @@
         <v>120</v>
       </c>
       <c r="I23">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J23">
         <v>0</v>
       </c>
       <c r="K23">
-        <v>0</v>
+        <v>73.3</v>
       </c>
       <c r="L23">
-        <v>0</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="M23">
         <v>0</v>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="O23">
         <v>0</v>
@@ -4602,22 +4449,22 @@
         <v>86.7</v>
       </c>
       <c r="I24">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="J24">
         <v>0</v>
       </c>
       <c r="K24">
-        <v>0</v>
+        <v>86.7</v>
       </c>
       <c r="L24">
-        <v>0</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="M24">
         <v>0</v>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="O24">
         <v>0</v>
@@ -4670,22 +4517,22 @@
         <v>106.7</v>
       </c>
       <c r="I25">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="J25">
         <v>0</v>
       </c>
       <c r="K25">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="L25">
-        <v>0</v>
+        <v>85.7</v>
       </c>
       <c r="M25">
         <v>0</v>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="O25">
         <v>0</v>
@@ -4738,22 +4585,22 @@
         <v>120</v>
       </c>
       <c r="I26">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="J26">
         <v>0</v>
       </c>
       <c r="K26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M26">
         <v>0</v>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O26">
         <v>0</v>
@@ -4806,22 +4653,22 @@
         <v>120</v>
       </c>
       <c r="I27">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="J27">
         <v>0</v>
       </c>
       <c r="K27">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="L27">
-        <v>0</v>
+        <v>94.3</v>
       </c>
       <c r="M27">
         <v>0</v>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O27">
         <v>0</v>
@@ -4874,22 +4721,22 @@
         <v>86.7</v>
       </c>
       <c r="I28">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="J28">
         <v>0</v>
       </c>
       <c r="K28">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="L28">
-        <v>0</v>
+        <v>54.3</v>
       </c>
       <c r="M28">
         <v>0</v>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="O28">
         <v>0</v>
@@ -4932,6 +4779,8 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="50.7109375" customWidth="1"/>
+    <col min="6" max="7" width="9.140625" style="2"/>
+    <col min="10" max="10" width="9.140625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -4982,10 +4831,10 @@
       <c r="E2">
         <v>16</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="2">
         <v>36</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="2">
         <v>64</v>
       </c>
       <c r="H2">
@@ -4994,7 +4843,7 @@
       <c r="I2">
         <v>0</v>
       </c>
-      <c r="J2">
+      <c r="J2" s="2">
         <v>0</v>
       </c>
     </row>
@@ -5009,24 +4858,24 @@
         <v>24</v>
       </c>
       <c r="D3">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E3">
-        <v>11</v>
-      </c>
-      <c r="F3">
-        <v>54.17</v>
-      </c>
-      <c r="G3">
-        <v>45.83</v>
+        <v>12</v>
+      </c>
+      <c r="F3" s="2">
+        <v>50</v>
+      </c>
+      <c r="G3" s="2">
+        <v>50</v>
       </c>
       <c r="H3">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="I3">
         <v>0</v>
       </c>
-      <c r="J3">
+      <c r="J3" s="2">
         <v>0</v>
       </c>
     </row>
@@ -5046,10 +4895,10 @@
       <c r="E4">
         <v>10</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="2">
         <v>60</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="2">
         <v>40</v>
       </c>
       <c r="H4">
@@ -5058,7 +4907,7 @@
       <c r="I4">
         <v>0</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="2">
         <v>0</v>
       </c>
     </row>
@@ -5073,30 +4922,30 @@
         <v>25</v>
       </c>
       <c r="D5">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E5">
-        <v>9</v>
-      </c>
-      <c r="F5">
-        <v>64</v>
-      </c>
-      <c r="G5">
-        <v>36</v>
+        <v>10</v>
+      </c>
+      <c r="F5" s="2">
+        <v>60</v>
+      </c>
+      <c r="G5" s="2">
+        <v>40</v>
       </c>
       <c r="H5">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="I5">
         <v>0</v>
       </c>
-      <c r="J5">
+      <c r="J5" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
         <v>54</v>
@@ -5105,30 +4954,30 @@
         <v>25</v>
       </c>
       <c r="D6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E6">
-        <v>9</v>
-      </c>
-      <c r="F6">
-        <v>64</v>
-      </c>
-      <c r="G6">
-        <v>36</v>
+        <v>8</v>
+      </c>
+      <c r="F6" s="2">
+        <v>68</v>
+      </c>
+      <c r="G6" s="2">
+        <v>32</v>
       </c>
       <c r="H6">
-        <v>7.1</v>
+        <v>6.6</v>
       </c>
       <c r="I6">
         <v>0</v>
       </c>
-      <c r="J6">
+      <c r="J6" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
         <v>55</v>
@@ -5142,19 +4991,19 @@
       <c r="E7">
         <v>8</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="2">
         <v>68</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="2">
         <v>32</v>
       </c>
       <c r="H7">
-        <v>6.6</v>
+        <v>7.3</v>
       </c>
       <c r="I7">
         <v>0</v>
       </c>
-      <c r="J7">
+      <c r="J7" s="2">
         <v>0</v>
       </c>
     </row>
@@ -5169,24 +5018,24 @@
         <v>25</v>
       </c>
       <c r="D8">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E8">
-        <v>6</v>
-      </c>
-      <c r="F8">
-        <v>76</v>
-      </c>
-      <c r="G8">
-        <v>24</v>
+        <v>8</v>
+      </c>
+      <c r="F8" s="2">
+        <v>68</v>
+      </c>
+      <c r="G8" s="2">
+        <v>32</v>
       </c>
       <c r="H8">
-        <v>7.3</v>
+        <v>6.9</v>
       </c>
       <c r="I8">
         <v>0</v>
       </c>
-      <c r="J8">
+      <c r="J8" s="2">
         <v>0</v>
       </c>
     </row>
@@ -5231,460 +5080,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E26"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="2" max="4" width="50.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>21330051920111</v>
-      </c>
-      <c r="B2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C2" t="s">
-        <v>81</v>
-      </c>
-      <c r="D2" t="s">
-        <v>101</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3">
-        <v>21330051920112</v>
-      </c>
-      <c r="B3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C3" t="s">
-        <v>82</v>
-      </c>
-      <c r="D3" t="s">
-        <v>102</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4">
-        <v>21330051920113</v>
-      </c>
-      <c r="B4" t="s">
-        <v>63</v>
-      </c>
-      <c r="C4" t="s">
-        <v>70</v>
-      </c>
-      <c r="D4" t="s">
-        <v>103</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5">
-        <v>21330051920114</v>
-      </c>
-      <c r="B5" t="s">
-        <v>64</v>
-      </c>
-      <c r="C5" t="s">
-        <v>83</v>
-      </c>
-      <c r="D5" t="s">
-        <v>104</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6">
-        <v>21330051920116</v>
-      </c>
-      <c r="B6" t="s">
-        <v>65</v>
-      </c>
-      <c r="C6" t="s">
-        <v>84</v>
-      </c>
-      <c r="D6" t="s">
-        <v>105</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7">
-        <v>21330051920117</v>
-      </c>
-      <c r="B7" t="s">
-        <v>66</v>
-      </c>
-      <c r="C7" t="s">
-        <v>85</v>
-      </c>
-      <c r="D7" t="s">
-        <v>106</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8">
-        <v>21330051920118</v>
-      </c>
-      <c r="B8" t="s">
-        <v>67</v>
-      </c>
-      <c r="C8" t="s">
-        <v>86</v>
-      </c>
-      <c r="D8" t="s">
-        <v>102</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9">
-        <v>21330051920119</v>
-      </c>
-      <c r="B9" t="s">
-        <v>68</v>
-      </c>
-      <c r="C9" t="s">
-        <v>87</v>
-      </c>
-      <c r="D9" t="s">
-        <v>107</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10">
-        <v>20330051920266</v>
-      </c>
-      <c r="B10" t="s">
-        <v>68</v>
-      </c>
-      <c r="C10" t="s">
-        <v>88</v>
-      </c>
-      <c r="D10" t="s">
-        <v>108</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11">
-        <v>21330051920120</v>
-      </c>
-      <c r="B11" t="s">
-        <v>68</v>
-      </c>
-      <c r="C11" t="s">
-        <v>89</v>
-      </c>
-      <c r="D11" t="s">
-        <v>109</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12">
-        <v>21330051920121</v>
-      </c>
-      <c r="B12" t="s">
-        <v>68</v>
-      </c>
-      <c r="C12" t="s">
-        <v>82</v>
-      </c>
-      <c r="D12" t="s">
-        <v>110</v>
-      </c>
-      <c r="E12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13">
-        <v>21330051920391</v>
-      </c>
-      <c r="B13" t="s">
-        <v>69</v>
-      </c>
-      <c r="C13" t="s">
-        <v>90</v>
-      </c>
-      <c r="D13" t="s">
-        <v>111</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14">
-        <v>21330051920122</v>
-      </c>
-      <c r="B14" t="s">
-        <v>70</v>
-      </c>
-      <c r="C14" t="s">
-        <v>68</v>
-      </c>
-      <c r="D14" t="s">
-        <v>112</v>
-      </c>
-      <c r="E14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15">
-        <v>20330051920346</v>
-      </c>
-      <c r="B15" t="s">
-        <v>70</v>
-      </c>
-      <c r="C15" t="s">
-        <v>91</v>
-      </c>
-      <c r="D15" t="s">
-        <v>113</v>
-      </c>
-      <c r="E15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16">
-        <v>21330051920123</v>
-      </c>
-      <c r="B16" t="s">
-        <v>71</v>
-      </c>
-      <c r="C16" t="s">
-        <v>92</v>
-      </c>
-      <c r="D16" t="s">
-        <v>114</v>
-      </c>
-      <c r="E16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17">
-        <v>21330051920125</v>
-      </c>
-      <c r="B17" t="s">
-        <v>72</v>
-      </c>
-      <c r="C17" t="s">
-        <v>67</v>
-      </c>
-      <c r="D17" t="s">
-        <v>115</v>
-      </c>
-      <c r="E17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18">
-        <v>21330051920126</v>
-      </c>
-      <c r="B18" t="s">
-        <v>73</v>
-      </c>
-      <c r="C18" t="s">
-        <v>93</v>
-      </c>
-      <c r="D18" t="s">
-        <v>116</v>
-      </c>
-      <c r="E18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19">
-        <v>21330051920127</v>
-      </c>
-      <c r="B19" t="s">
-        <v>74</v>
-      </c>
-      <c r="C19" t="s">
-        <v>94</v>
-      </c>
-      <c r="D19" t="s">
-        <v>117</v>
-      </c>
-      <c r="E19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20">
-        <v>21330051920129</v>
-      </c>
-      <c r="C20" t="s">
-        <v>95</v>
-      </c>
-      <c r="D20" t="s">
-        <v>118</v>
-      </c>
-      <c r="E20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21">
-        <v>21330051920130</v>
-      </c>
-      <c r="B21" t="s">
-        <v>75</v>
-      </c>
-      <c r="C21" t="s">
-        <v>96</v>
-      </c>
-      <c r="D21" t="s">
-        <v>119</v>
-      </c>
-      <c r="E21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22">
-        <v>21330051920131</v>
-      </c>
-      <c r="B22" t="s">
-        <v>76</v>
-      </c>
-      <c r="C22" t="s">
-        <v>97</v>
-      </c>
-      <c r="D22" t="s">
-        <v>120</v>
-      </c>
-      <c r="E22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23">
-        <v>18330051920377</v>
-      </c>
-      <c r="B23" t="s">
-        <v>77</v>
-      </c>
-      <c r="C23" t="s">
-        <v>98</v>
-      </c>
-      <c r="D23" t="s">
-        <v>121</v>
-      </c>
-      <c r="E23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24">
-        <v>21330051920132</v>
-      </c>
-      <c r="B24" t="s">
-        <v>78</v>
-      </c>
-      <c r="C24" t="s">
-        <v>99</v>
-      </c>
-      <c r="D24" t="s">
-        <v>122</v>
-      </c>
-      <c r="E24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25">
-        <v>20330051920152</v>
-      </c>
-      <c r="B25" t="s">
-        <v>79</v>
-      </c>
-      <c r="C25" t="s">
-        <v>62</v>
-      </c>
-      <c r="D25" t="s">
-        <v>123</v>
-      </c>
-      <c r="E25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26">
-        <v>21330051920133</v>
-      </c>
-      <c r="B26" t="s">
-        <v>80</v>
-      </c>
-      <c r="C26" t="s">
-        <v>100</v>
-      </c>
-      <c r="D26" t="s">
-        <v>124</v>
-      </c>
-      <c r="E26">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5722,10 +5118,10 @@
         <v>61</v>
       </c>
       <c r="C2" t="s">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="D2" t="s">
-        <v>101</v>
+        <v>69</v>
       </c>
       <c r="E2" t="s">
         <v>10</v>
@@ -5745,10 +5141,10 @@
         <v>61</v>
       </c>
       <c r="C3" t="s">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="D3" t="s">
-        <v>101</v>
+        <v>69</v>
       </c>
       <c r="E3" t="s">
         <v>11</v>
@@ -5762,22 +5158,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920122</v>
+        <v>20330051920152</v>
       </c>
       <c r="B4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D4" t="s">
         <v>70</v>
       </c>
-      <c r="C4" t="s">
-        <v>68</v>
-      </c>
-      <c r="D4" t="s">
-        <v>112</v>
-      </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -5785,22 +5181,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920122</v>
+        <v>20330051920152</v>
       </c>
       <c r="B5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C5" t="s">
+        <v>66</v>
+      </c>
+      <c r="D5" t="s">
         <v>70</v>
       </c>
-      <c r="C5" t="s">
-        <v>68</v>
-      </c>
-      <c r="D5" t="s">
-        <v>112</v>
-      </c>
       <c r="E5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -5808,16 +5204,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>18330051920377</v>
+        <v>21330051920114</v>
       </c>
       <c r="B6" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C6" t="s">
-        <v>98</v>
+        <v>67</v>
       </c>
       <c r="D6" t="s">
-        <v>121</v>
+        <v>71</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -5831,116 +5227,24 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>18330051920377</v>
+        <v>21330051920118</v>
       </c>
       <c r="B7" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="C7" t="s">
-        <v>98</v>
+        <v>68</v>
       </c>
       <c r="D7" t="s">
-        <v>121</v>
+        <v>72</v>
       </c>
       <c r="E7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>20330051920152</v>
-      </c>
-      <c r="B8" t="s">
-        <v>79</v>
-      </c>
-      <c r="C8" t="s">
-        <v>62</v>
-      </c>
-      <c r="D8" t="s">
-        <v>123</v>
-      </c>
-      <c r="E8" t="s">
-        <v>5</v>
-      </c>
-      <c r="F8" t="s">
-        <v>53</v>
-      </c>
-      <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>20330051920152</v>
-      </c>
-      <c r="B9" t="s">
-        <v>79</v>
-      </c>
-      <c r="C9" t="s">
-        <v>62</v>
-      </c>
-      <c r="D9" t="s">
-        <v>123</v>
-      </c>
-      <c r="E9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" t="s">
-        <v>50</v>
-      </c>
-      <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>21330051920114</v>
-      </c>
-      <c r="B10" t="s">
-        <v>64</v>
-      </c>
-      <c r="C10" t="s">
-        <v>83</v>
-      </c>
-      <c r="D10" t="s">
-        <v>104</v>
-      </c>
-      <c r="E10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" t="s">
-        <v>50</v>
-      </c>
-      <c r="G10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>21330051920121</v>
-      </c>
-      <c r="B11" t="s">
-        <v>68</v>
-      </c>
-      <c r="C11" t="s">
-        <v>82</v>
-      </c>
-      <c r="D11" t="s">
-        <v>110</v>
-      </c>
-      <c r="E11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11" t="s">
-        <v>51</v>
-      </c>
-      <c r="G11">
         <v>5</v>
       </c>
     </row>

--- a/grupos/4APV - Estadisticos 20222.xlsx
+++ b/grupos/4APV - Estadisticos 20222.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="70">
   <si>
     <t>Materia</t>
   </si>
@@ -203,9 +203,6 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>BARRAGAN</t>
-  </si>
-  <si>
     <t>TRUJILLO</t>
   </si>
   <si>
@@ -215,9 +212,6 @@
     <t>FLORES</t>
   </si>
   <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
     <t>CASTRO</t>
   </si>
   <si>
@@ -225,9 +219,6 @@
   </si>
   <si>
     <t>VILLA</t>
-  </si>
-  <si>
-    <t>KAREN ITZEL</t>
   </si>
   <si>
     <t>MARIA DEL CARMEN</t>
@@ -766,7 +757,7 @@
         <v>9</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K4">
         <v>10</v>
@@ -855,7 +846,7 @@
         <v>6</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K5">
         <v>6</v>
@@ -897,7 +888,7 @@
         <v>6</v>
       </c>
       <c r="X5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y5">
         <v>7</v>
@@ -944,7 +935,7 @@
         <v>5</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K6">
         <v>5</v>
@@ -1033,7 +1024,7 @@
         <v>6</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K7">
         <v>7</v>
@@ -1075,7 +1066,7 @@
         <v>8</v>
       </c>
       <c r="X7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y7">
         <v>8</v>
@@ -1122,7 +1113,7 @@
         <v>5</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K8">
         <v>5</v>
@@ -1211,7 +1202,7 @@
         <v>10</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K9">
         <v>10</v>
@@ -1300,7 +1291,7 @@
         <v>5</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K10">
         <v>5</v>
@@ -1342,7 +1333,7 @@
         <v>5</v>
       </c>
       <c r="X10">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y10">
         <v>6</v>
@@ -1389,7 +1380,7 @@
         <v>8</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K11">
         <v>7</v>
@@ -1431,7 +1422,7 @@
         <v>8</v>
       </c>
       <c r="X11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y11">
         <v>7</v>
@@ -1478,7 +1469,7 @@
         <v>6</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K12">
         <v>6</v>
@@ -1567,7 +1558,7 @@
         <v>7</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K13">
         <v>9</v>
@@ -1656,7 +1647,7 @@
         <v>5</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K14">
         <v>6</v>
@@ -1698,7 +1689,7 @@
         <v>5</v>
       </c>
       <c r="X14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y14">
         <v>6</v>
@@ -1745,7 +1736,7 @@
         <v>6</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K15">
         <v>9</v>
@@ -1787,7 +1778,7 @@
         <v>8</v>
       </c>
       <c r="X15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y15">
         <v>9</v>
@@ -1834,7 +1825,7 @@
         <v>7</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K16">
         <v>6</v>
@@ -1923,7 +1914,7 @@
         <v>7</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K17">
         <v>7</v>
@@ -1965,7 +1956,7 @@
         <v>8</v>
       </c>
       <c r="X17">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y17">
         <v>8</v>
@@ -2009,7 +2000,7 @@
         <v>5</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K18">
         <v>5</v>
@@ -2089,7 +2080,7 @@
         <v>7</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K19">
         <v>7</v>
@@ -2131,7 +2122,7 @@
         <v>9</v>
       </c>
       <c r="X19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y19">
         <v>8</v>
@@ -2178,7 +2169,7 @@
         <v>5</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K20">
         <v>6</v>
@@ -2267,7 +2258,7 @@
         <v>6</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K21">
         <v>6</v>
@@ -2309,7 +2300,7 @@
         <v>7</v>
       </c>
       <c r="X21">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y21">
         <v>7</v>
@@ -2356,7 +2347,7 @@
         <v>5</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K22">
         <v>5</v>
@@ -2445,7 +2436,7 @@
         <v>5</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K23">
         <v>5</v>
@@ -2487,7 +2478,7 @@
         <v>5</v>
       </c>
       <c r="X23">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y23">
         <v>5</v>
@@ -2534,7 +2525,7 @@
         <v>7</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K24">
         <v>7</v>
@@ -2623,7 +2614,7 @@
         <v>6</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K25">
         <v>6</v>
@@ -2665,7 +2656,7 @@
         <v>6</v>
       </c>
       <c r="X25">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y25">
         <v>7</v>
@@ -2712,7 +2703,7 @@
         <v>9</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K26">
         <v>9</v>
@@ -2801,7 +2792,7 @@
         <v>6</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K27">
         <v>5</v>
@@ -2843,7 +2834,7 @@
         <v>5</v>
       </c>
       <c r="X27">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y27">
         <v>7</v>
@@ -2890,7 +2881,7 @@
         <v>6</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K28">
         <v>5</v>
@@ -3101,7 +3092,7 @@
         <v>100</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="K4">
         <v>100</v>
@@ -3169,7 +3160,7 @@
         <v>95</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K5">
         <v>86.7</v>
@@ -3237,7 +3228,7 @@
         <v>0</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="K6">
         <v>73.3</v>
@@ -3305,7 +3296,7 @@
         <v>85</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="K7">
         <v>93.3</v>
@@ -3373,7 +3364,7 @@
         <v>0</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="K8">
         <v>80</v>
@@ -3441,7 +3432,7 @@
         <v>100</v>
       </c>
       <c r="J9">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="K9">
         <v>100</v>
@@ -3509,7 +3500,7 @@
         <v>15</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="K10">
         <v>73.3</v>
@@ -3577,7 +3568,7 @@
         <v>100</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="K11">
         <v>100</v>
@@ -3645,7 +3636,7 @@
         <v>100</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="K12">
         <v>86.7</v>
@@ -3713,7 +3704,7 @@
         <v>100</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="K13">
         <v>100</v>
@@ -3781,7 +3772,7 @@
         <v>15</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="K14">
         <v>80</v>
@@ -3849,7 +3840,7 @@
         <v>100</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="K15">
         <v>100</v>
@@ -3917,7 +3908,7 @@
         <v>75</v>
       </c>
       <c r="J16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K16">
         <v>86.7</v>
@@ -3985,7 +3976,7 @@
         <v>90</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K17">
         <v>93.3</v>
@@ -4112,7 +4103,7 @@
         <v>90</v>
       </c>
       <c r="J19">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="K19">
         <v>100</v>
@@ -4180,7 +4171,7 @@
         <v>20</v>
       </c>
       <c r="J20">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="K20">
         <v>86.7</v>
@@ -4248,7 +4239,7 @@
         <v>75</v>
       </c>
       <c r="J21">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="K21">
         <v>73.3</v>
@@ -4316,7 +4307,7 @@
         <v>40</v>
       </c>
       <c r="J22">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="K22">
         <v>80</v>
@@ -4384,7 +4375,7 @@
         <v>15</v>
       </c>
       <c r="J23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K23">
         <v>73.3</v>
@@ -4452,7 +4443,7 @@
         <v>90</v>
       </c>
       <c r="J24">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="K24">
         <v>86.7</v>
@@ -4520,7 +4511,7 @@
         <v>90</v>
       </c>
       <c r="J25">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="K25">
         <v>93.3</v>
@@ -4588,7 +4579,7 @@
         <v>95</v>
       </c>
       <c r="J26">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="K26">
         <v>100</v>
@@ -4656,7 +4647,7 @@
         <v>80</v>
       </c>
       <c r="J27">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="K27">
         <v>93.3</v>
@@ -4724,7 +4715,7 @@
         <v>45</v>
       </c>
       <c r="J28">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="K28">
         <v>93.3</v>
@@ -4954,19 +4945,19 @@
         <v>25</v>
       </c>
       <c r="D6">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F6" s="2">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="G6" s="2">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="H6">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -5080,7 +5071,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5112,22 +5103,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920111</v>
+        <v>20330051920152</v>
       </c>
       <c r="B2" t="s">
         <v>61</v>
       </c>
       <c r="C2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -5135,22 +5126,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920111</v>
+        <v>20330051920152</v>
       </c>
       <c r="B3" t="s">
         <v>61</v>
       </c>
       <c r="C3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -5158,22 +5149,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920152</v>
+        <v>21330051920114</v>
       </c>
       <c r="B4" t="s">
         <v>62</v>
       </c>
       <c r="C4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -5181,70 +5172,24 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920152</v>
+        <v>21330051920118</v>
       </c>
       <c r="B5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C5" t="s">
         <v>66</v>
       </c>
       <c r="D5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>21330051920114</v>
-      </c>
-      <c r="B6" t="s">
-        <v>63</v>
-      </c>
-      <c r="C6" t="s">
-        <v>67</v>
-      </c>
-      <c r="D6" t="s">
-        <v>71</v>
-      </c>
-      <c r="E6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" t="s">
-        <v>50</v>
-      </c>
-      <c r="G6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>21330051920118</v>
-      </c>
-      <c r="B7" t="s">
-        <v>64</v>
-      </c>
-      <c r="C7" t="s">
-        <v>68</v>
-      </c>
-      <c r="D7" t="s">
-        <v>72</v>
-      </c>
-      <c r="E7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" t="s">
-        <v>51</v>
-      </c>
-      <c r="G7">
         <v>5</v>
       </c>
     </row>

--- a/grupos/4APV - Estadisticos 20222.xlsx
+++ b/grupos/4APV - Estadisticos 20222.xlsx
@@ -766,7 +766,7 @@
         <v>10</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N4">
         <v>7</v>
@@ -855,7 +855,7 @@
         <v>8</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N5">
         <v>5</v>
@@ -897,7 +897,7 @@
         <v>7</v>
       </c>
       <c r="AA5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB5">
         <v>5</v>
@@ -944,7 +944,7 @@
         <v>6</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N6">
         <v>5</v>
@@ -1033,7 +1033,7 @@
         <v>9</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N7">
         <v>7</v>
@@ -1122,7 +1122,7 @@
         <v>7</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N8">
         <v>6</v>
@@ -1211,7 +1211,7 @@
         <v>10</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N9">
         <v>9</v>
@@ -1300,7 +1300,7 @@
         <v>6</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N10">
         <v>7</v>
@@ -1389,7 +1389,7 @@
         <v>9</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N11">
         <v>5</v>
@@ -1478,7 +1478,7 @@
         <v>9</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N12">
         <v>5</v>
@@ -1567,7 +1567,7 @@
         <v>9</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N13">
         <v>6</v>
@@ -1609,7 +1609,7 @@
         <v>9</v>
       </c>
       <c r="AA13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB13">
         <v>8</v>
@@ -1656,7 +1656,7 @@
         <v>6</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N14">
         <v>6</v>
@@ -1745,7 +1745,7 @@
         <v>10</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N15">
         <v>7</v>
@@ -1787,7 +1787,7 @@
         <v>10</v>
       </c>
       <c r="AA15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB15">
         <v>6</v>
@@ -1834,7 +1834,7 @@
         <v>8</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N16">
         <v>5</v>
@@ -1923,7 +1923,7 @@
         <v>8</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N17">
         <v>5</v>
@@ -2009,7 +2009,7 @@
         <v>5</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="O18">
         <v>-1</v>
@@ -2089,7 +2089,7 @@
         <v>7</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N19">
         <v>7</v>
@@ -2178,7 +2178,7 @@
         <v>6</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N20">
         <v>5</v>
@@ -2267,7 +2267,7 @@
         <v>6</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N21">
         <v>6</v>
@@ -2356,7 +2356,7 @@
         <v>6</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N22">
         <v>6</v>
@@ -2445,7 +2445,7 @@
         <v>6</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N23">
         <v>7</v>
@@ -2534,7 +2534,7 @@
         <v>7</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N24">
         <v>7</v>
@@ -2576,7 +2576,7 @@
         <v>7</v>
       </c>
       <c r="AA24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB24">
         <v>7</v>
@@ -2623,7 +2623,7 @@
         <v>7</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N25">
         <v>5</v>
@@ -2712,7 +2712,7 @@
         <v>10</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N26">
         <v>7</v>
@@ -2801,7 +2801,7 @@
         <v>7</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N27">
         <v>7</v>
@@ -2890,7 +2890,7 @@
         <v>5</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N28">
         <v>5</v>
@@ -3101,7 +3101,7 @@
         <v>100</v>
       </c>
       <c r="M4">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="N4">
         <v>100</v>
@@ -3169,7 +3169,7 @@
         <v>85.7</v>
       </c>
       <c r="M5">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="N5">
         <v>95</v>
@@ -3237,7 +3237,7 @@
         <v>42.9</v>
       </c>
       <c r="M6">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="N6">
         <v>20</v>
@@ -3305,7 +3305,7 @@
         <v>85.7</v>
       </c>
       <c r="M7">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="N7">
         <v>95</v>
@@ -3373,7 +3373,7 @@
         <v>68.59999999999999</v>
       </c>
       <c r="M8">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="N8">
         <v>70</v>
@@ -3441,7 +3441,7 @@
         <v>100</v>
       </c>
       <c r="M9">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="N9">
         <v>95</v>
@@ -3509,7 +3509,7 @@
         <v>68.59999999999999</v>
       </c>
       <c r="M10">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="N10">
         <v>90</v>
@@ -3577,7 +3577,7 @@
         <v>100</v>
       </c>
       <c r="M11">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="N11">
         <v>100</v>
@@ -3645,7 +3645,7 @@
         <v>80</v>
       </c>
       <c r="M12">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="N12">
         <v>90</v>
@@ -3713,7 +3713,7 @@
         <v>100</v>
       </c>
       <c r="M13">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="N13">
         <v>95</v>
@@ -3781,7 +3781,7 @@
         <v>68.59999999999999</v>
       </c>
       <c r="M14">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="N14">
         <v>85</v>
@@ -3849,7 +3849,7 @@
         <v>97.09999999999999</v>
       </c>
       <c r="M15">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="N15">
         <v>100</v>
@@ -3917,7 +3917,7 @@
         <v>82.90000000000001</v>
       </c>
       <c r="M16">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="N16">
         <v>80</v>
@@ -3985,7 +3985,7 @@
         <v>100</v>
       </c>
       <c r="M17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N17">
         <v>95</v>
@@ -4112,7 +4112,7 @@
         <v>94.3</v>
       </c>
       <c r="M19">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="N19">
         <v>90</v>
@@ -4180,7 +4180,7 @@
         <v>54.3</v>
       </c>
       <c r="M20">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="N20">
         <v>55</v>
@@ -4248,7 +4248,7 @@
         <v>57.1</v>
       </c>
       <c r="M21">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="N21">
         <v>55</v>
@@ -4316,7 +4316,7 @@
         <v>65.7</v>
       </c>
       <c r="M22">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="N22">
         <v>50</v>
@@ -4384,7 +4384,7 @@
         <v>68.59999999999999</v>
       </c>
       <c r="M23">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="N23">
         <v>85</v>
@@ -4452,7 +4452,7 @@
         <v>88.59999999999999</v>
       </c>
       <c r="M24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N24">
         <v>95</v>
@@ -4520,7 +4520,7 @@
         <v>85.7</v>
       </c>
       <c r="M25">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="N25">
         <v>85</v>
@@ -4588,7 +4588,7 @@
         <v>100</v>
       </c>
       <c r="M26">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="N26">
         <v>100</v>
@@ -4656,7 +4656,7 @@
         <v>94.3</v>
       </c>
       <c r="M27">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="N27">
         <v>100</v>
@@ -4724,7 +4724,7 @@
         <v>54.3</v>
       </c>
       <c r="M28">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="N28">
         <v>80</v>
@@ -4817,16 +4817,16 @@
         <v>25</v>
       </c>
       <c r="D2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F2" s="2">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="G2" s="2">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="H2">
         <v>6.1</v>

--- a/grupos/4APV - Estadisticos 20222.xlsx
+++ b/grupos/4APV - Estadisticos 20222.xlsx
@@ -772,7 +772,7 @@
         <v>7</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P4">
         <v>-1</v>
@@ -814,7 +814,7 @@
         <v>9</v>
       </c>
       <c r="AC4">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:29">
@@ -1128,7 +1128,7 @@
         <v>6</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P8">
         <v>-1</v>
@@ -1217,7 +1217,7 @@
         <v>9</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P9">
         <v>-1</v>
@@ -1395,7 +1395,7 @@
         <v>5</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P11">
         <v>-1</v>
@@ -1573,7 +1573,7 @@
         <v>6</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P13">
         <v>-1</v>
@@ -1662,7 +1662,7 @@
         <v>6</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P14">
         <v>-1</v>
@@ -1751,7 +1751,7 @@
         <v>7</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P15">
         <v>-1</v>
@@ -1793,7 +1793,7 @@
         <v>6</v>
       </c>
       <c r="AC15">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:29">
@@ -2095,7 +2095,7 @@
         <v>7</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P19">
         <v>-1</v>
@@ -2137,7 +2137,7 @@
         <v>7</v>
       </c>
       <c r="AC19">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:29">
@@ -2540,7 +2540,7 @@
         <v>7</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P24">
         <v>-1</v>
@@ -2582,7 +2582,7 @@
         <v>7</v>
       </c>
       <c r="AC24">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25" spans="1:29">
@@ -2629,7 +2629,7 @@
         <v>5</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P25">
         <v>-1</v>
@@ -2718,7 +2718,7 @@
         <v>7</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P26">
         <v>-1</v>
@@ -2807,7 +2807,7 @@
         <v>7</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P27">
         <v>-1</v>
@@ -2849,7 +2849,7 @@
         <v>7</v>
       </c>
       <c r="AC27">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28" spans="1:29">
@@ -4893,7 +4893,7 @@
         <v>40</v>
       </c>
       <c r="H4">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
       <c r="I4">
         <v>0</v>

--- a/grupos/4APV - Estadisticos 20222.xlsx
+++ b/grupos/4APV - Estadisticos 20222.xlsx
@@ -861,7 +861,7 @@
         <v>5</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P5">
         <v>-1</v>
@@ -950,7 +950,7 @@
         <v>5</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P6">
         <v>-1</v>
@@ -1039,7 +1039,7 @@
         <v>7</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P7">
         <v>-1</v>
@@ -1081,7 +1081,7 @@
         <v>7</v>
       </c>
       <c r="AC7">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:29">
@@ -1306,7 +1306,7 @@
         <v>7</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P10">
         <v>-1</v>
@@ -1348,7 +1348,7 @@
         <v>6</v>
       </c>
       <c r="AC10">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:29">
@@ -1484,7 +1484,7 @@
         <v>5</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P12">
         <v>-1</v>
@@ -1526,7 +1526,7 @@
         <v>7</v>
       </c>
       <c r="AC12">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:29">
@@ -1840,7 +1840,7 @@
         <v>5</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P16">
         <v>-1</v>
@@ -1929,7 +1929,7 @@
         <v>5</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P17">
         <v>-1</v>
@@ -2012,7 +2012,7 @@
         <v>0</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P18">
         <v>-1</v>
@@ -2184,7 +2184,7 @@
         <v>5</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P20">
         <v>-1</v>
@@ -2273,7 +2273,7 @@
         <v>6</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P21">
         <v>-1</v>
@@ -2362,7 +2362,7 @@
         <v>6</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P22">
         <v>-1</v>
@@ -2451,7 +2451,7 @@
         <v>7</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P23">
         <v>-1</v>
@@ -2896,7 +2896,7 @@
         <v>5</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P28">
         <v>-1</v>
@@ -2938,7 +2938,7 @@
         <v>5</v>
       </c>
       <c r="AC28">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -3107,7 +3107,7 @@
         <v>100</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="P4">
         <v>0</v>
@@ -3175,7 +3175,7 @@
         <v>95</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="P5">
         <v>0</v>
@@ -3243,7 +3243,7 @@
         <v>20</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="P6">
         <v>0</v>
@@ -3311,7 +3311,7 @@
         <v>95</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="P7">
         <v>0</v>
@@ -3379,7 +3379,7 @@
         <v>70</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="P8">
         <v>0</v>
@@ -3447,7 +3447,7 @@
         <v>95</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="P9">
         <v>0</v>
@@ -3515,7 +3515,7 @@
         <v>90</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="P10">
         <v>0</v>
@@ -3583,7 +3583,7 @@
         <v>100</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="P11">
         <v>0</v>
@@ -3651,7 +3651,7 @@
         <v>90</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="P12">
         <v>0</v>
@@ -3719,7 +3719,7 @@
         <v>95</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="P13">
         <v>0</v>
@@ -3787,7 +3787,7 @@
         <v>85</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="P14">
         <v>0</v>
@@ -3855,7 +3855,7 @@
         <v>100</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="P15">
         <v>0</v>
@@ -3923,7 +3923,7 @@
         <v>80</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="P16">
         <v>0</v>
@@ -3991,7 +3991,7 @@
         <v>95</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="P17">
         <v>0</v>
@@ -4053,7 +4053,7 @@
         <v>0</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="P18">
         <v>0</v>
@@ -4118,7 +4118,7 @@
         <v>90</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="P19">
         <v>0</v>
@@ -4186,7 +4186,7 @@
         <v>55</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="P20">
         <v>0</v>
@@ -4254,7 +4254,7 @@
         <v>55</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="P21">
         <v>0</v>
@@ -4322,7 +4322,7 @@
         <v>50</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="P22">
         <v>0</v>
@@ -4390,7 +4390,7 @@
         <v>85</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="P23">
         <v>0</v>
@@ -4458,7 +4458,7 @@
         <v>95</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="P24">
         <v>0</v>
@@ -4526,7 +4526,7 @@
         <v>85</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="P25">
         <v>0</v>
@@ -4594,7 +4594,7 @@
         <v>100</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="P26">
         <v>0</v>
@@ -4662,7 +4662,7 @@
         <v>100</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="P27">
         <v>0</v>
@@ -4730,7 +4730,7 @@
         <v>80</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="P28">
         <v>0</v>
@@ -4881,19 +4881,19 @@
         <v>25</v>
       </c>
       <c r="D4">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E4">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F4" s="2">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="G4" s="2">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="H4">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
       <c r="I4">
         <v>0</v>

--- a/grupos/4APV - Estadisticos 20222.xlsx
+++ b/grupos/4APV - Estadisticos 20222.xlsx
@@ -3071,7 +3071,7 @@
         <v>100</v>
       </c>
       <c r="C4">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="D4">
         <v>100</v>
@@ -3080,19 +3080,19 @@
         <v>100</v>
       </c>
       <c r="F4">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="G4">
         <v>100</v>
       </c>
       <c r="H4">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I4">
         <v>100</v>
       </c>
       <c r="J4">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="K4">
         <v>100</v>
@@ -3101,34 +3101,34 @@
         <v>100</v>
       </c>
       <c r="M4">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="N4">
         <v>100</v>
       </c>
       <c r="O4">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:22">
@@ -3139,7 +3139,7 @@
         <v>85</v>
       </c>
       <c r="C5">
-        <v>115</v>
+        <v>95.8</v>
       </c>
       <c r="D5">
         <v>100</v>
@@ -3148,55 +3148,55 @@
         <v>86.7</v>
       </c>
       <c r="F5">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="G5">
         <v>100</v>
       </c>
       <c r="H5">
+        <v>77.8</v>
+      </c>
+      <c r="I5">
+        <v>90</v>
+      </c>
+      <c r="J5">
+        <v>93.5</v>
+      </c>
+      <c r="K5">
         <v>93.3</v>
       </c>
-      <c r="I5">
-        <v>95</v>
-      </c>
-      <c r="J5">
-        <v>100</v>
-      </c>
-      <c r="K5">
-        <v>86.7</v>
-      </c>
       <c r="L5">
-        <v>85.7</v>
+        <v>86.2</v>
       </c>
       <c r="M5">
-        <v>105</v>
+        <v>93.2</v>
       </c>
       <c r="N5">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="O5">
-        <v>120</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>93.5</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>86.2</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>93.2</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>88.90000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:22">
@@ -3207,7 +3207,7 @@
         <v>70</v>
       </c>
       <c r="C6">
-        <v>115</v>
+        <v>95.8</v>
       </c>
       <c r="D6">
         <v>73.3</v>
@@ -3216,55 +3216,55 @@
         <v>63.3</v>
       </c>
       <c r="F6">
-        <v>75</v>
+        <v>68.2</v>
       </c>
       <c r="G6">
         <v>70</v>
       </c>
       <c r="H6">
-        <v>80</v>
+        <v>66.7</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="J6">
-        <v>75</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="K6">
         <v>73.3</v>
       </c>
       <c r="L6">
-        <v>42.9</v>
+        <v>52.3</v>
       </c>
       <c r="M6">
-        <v>75</v>
+        <v>68.2</v>
       </c>
       <c r="N6">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="O6">
-        <v>120</v>
+        <v>83.3</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>73.3</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>52.3</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>68.2</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>83.3</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -3275,7 +3275,7 @@
         <v>85</v>
       </c>
       <c r="C7">
-        <v>115</v>
+        <v>95.8</v>
       </c>
       <c r="D7">
         <v>100</v>
@@ -3284,55 +3284,55 @@
         <v>83.3</v>
       </c>
       <c r="F7">
-        <v>80</v>
+        <v>72.7</v>
       </c>
       <c r="G7">
         <v>100</v>
       </c>
       <c r="H7">
-        <v>93.3</v>
+        <v>77.8</v>
       </c>
       <c r="I7">
         <v>85</v>
       </c>
       <c r="J7">
-        <v>110</v>
+        <v>97.8</v>
       </c>
       <c r="K7">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="L7">
-        <v>85.7</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="M7">
-        <v>95</v>
+        <v>79.5</v>
       </c>
       <c r="N7">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="O7">
-        <v>120</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>97.8</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>79.5</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>88.90000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -3343,7 +3343,7 @@
         <v>70</v>
       </c>
       <c r="C8">
-        <v>115</v>
+        <v>95.8</v>
       </c>
       <c r="D8">
         <v>80</v>
@@ -3352,55 +3352,55 @@
         <v>63.3</v>
       </c>
       <c r="F8">
-        <v>90</v>
+        <v>81.8</v>
       </c>
       <c r="G8">
         <v>85</v>
       </c>
       <c r="H8">
-        <v>100</v>
+        <v>83.3</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="J8">
-        <v>95</v>
+        <v>91.3</v>
       </c>
       <c r="K8">
         <v>80</v>
       </c>
       <c r="L8">
-        <v>68.59999999999999</v>
+        <v>66.2</v>
       </c>
       <c r="M8">
         <v>75</v>
       </c>
       <c r="N8">
-        <v>70</v>
+        <v>77.5</v>
       </c>
       <c r="O8">
-        <v>120</v>
+        <v>91.7</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>91.3</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>66.2</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>77.5</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>91.7</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -3411,7 +3411,7 @@
         <v>75</v>
       </c>
       <c r="C9">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="D9">
         <v>100</v>
@@ -3420,55 +3420,55 @@
         <v>96.7</v>
       </c>
       <c r="F9">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="G9">
         <v>100</v>
       </c>
       <c r="H9">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I9">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="J9">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="K9">
         <v>100</v>
       </c>
       <c r="L9">
-        <v>100</v>
+        <v>98.5</v>
       </c>
       <c r="M9">
-        <v>110</v>
+        <v>95.5</v>
       </c>
       <c r="N9">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="O9">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>98.5</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>95.5</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -3479,7 +3479,7 @@
         <v>70</v>
       </c>
       <c r="C10">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="D10">
         <v>86.7</v>
@@ -3488,55 +3488,55 @@
         <v>83.3</v>
       </c>
       <c r="F10">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="G10">
         <v>90</v>
       </c>
       <c r="H10">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I10">
-        <v>15</v>
+        <v>42.5</v>
       </c>
       <c r="J10">
-        <v>105</v>
+        <v>97.8</v>
       </c>
       <c r="K10">
-        <v>73.3</v>
+        <v>80</v>
       </c>
       <c r="L10">
-        <v>68.59999999999999</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="M10">
-        <v>75</v>
+        <v>79.5</v>
       </c>
       <c r="N10">
         <v>90</v>
       </c>
       <c r="O10">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>42.5</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>97.8</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>79.5</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -3547,7 +3547,7 @@
         <v>100</v>
       </c>
       <c r="C11">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="D11">
         <v>100</v>
@@ -3556,19 +3556,19 @@
         <v>100</v>
       </c>
       <c r="F11">
-        <v>105</v>
+        <v>95.5</v>
       </c>
       <c r="G11">
         <v>100</v>
       </c>
       <c r="H11">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I11">
         <v>100</v>
       </c>
       <c r="J11">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="K11">
         <v>100</v>
@@ -3577,34 +3577,34 @@
         <v>100</v>
       </c>
       <c r="M11">
-        <v>110</v>
+        <v>97.7</v>
       </c>
       <c r="N11">
         <v>100</v>
       </c>
       <c r="O11">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>97.7</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -3615,7 +3615,7 @@
         <v>70</v>
       </c>
       <c r="C12">
-        <v>115</v>
+        <v>95.8</v>
       </c>
       <c r="D12">
         <v>73.3</v>
@@ -3624,55 +3624,55 @@
         <v>73.3</v>
       </c>
       <c r="F12">
-        <v>75</v>
+        <v>68.2</v>
       </c>
       <c r="G12">
         <v>70</v>
       </c>
       <c r="H12">
-        <v>93.3</v>
+        <v>77.8</v>
       </c>
       <c r="I12">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="J12">
-        <v>105</v>
+        <v>95.7</v>
       </c>
       <c r="K12">
-        <v>86.7</v>
+        <v>80</v>
       </c>
       <c r="L12">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="M12">
+        <v>77.3</v>
+      </c>
+      <c r="N12">
         <v>80</v>
       </c>
-      <c r="M12">
-        <v>95</v>
-      </c>
-      <c r="N12">
-        <v>90</v>
-      </c>
       <c r="O12">
-        <v>120</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>95.7</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>77.3</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>88.90000000000001</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -3683,7 +3683,7 @@
         <v>100</v>
       </c>
       <c r="C13">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="D13">
         <v>100</v>
@@ -3692,19 +3692,19 @@
         <v>100</v>
       </c>
       <c r="F13">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="G13">
         <v>85</v>
       </c>
       <c r="H13">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I13">
         <v>100</v>
       </c>
       <c r="J13">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="K13">
         <v>100</v>
@@ -3713,34 +3713,34 @@
         <v>100</v>
       </c>
       <c r="M13">
-        <v>105</v>
+        <v>93.2</v>
       </c>
       <c r="N13">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="O13">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>93.2</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14" spans="1:22">
@@ -3751,7 +3751,7 @@
         <v>70</v>
       </c>
       <c r="C14">
-        <v>115</v>
+        <v>95.8</v>
       </c>
       <c r="D14">
         <v>80</v>
@@ -3760,55 +3760,55 @@
         <v>63.3</v>
       </c>
       <c r="F14">
-        <v>85</v>
+        <v>77.3</v>
       </c>
       <c r="G14">
         <v>85</v>
       </c>
       <c r="H14">
-        <v>93.3</v>
+        <v>77.8</v>
       </c>
       <c r="I14">
-        <v>15</v>
+        <v>42.5</v>
       </c>
       <c r="J14">
-        <v>75</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="K14">
         <v>80</v>
       </c>
       <c r="L14">
-        <v>68.59999999999999</v>
+        <v>66.2</v>
       </c>
       <c r="M14">
-        <v>85</v>
+        <v>77.3</v>
       </c>
       <c r="N14">
         <v>85</v>
       </c>
       <c r="O14">
-        <v>120</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>42.5</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>66.2</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>77.3</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>88.90000000000001</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -3819,7 +3819,7 @@
         <v>100</v>
       </c>
       <c r="C15">
-        <v>115</v>
+        <v>95.8</v>
       </c>
       <c r="D15">
         <v>100</v>
@@ -3828,55 +3828,55 @@
         <v>86.7</v>
       </c>
       <c r="F15">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="G15">
         <v>100</v>
       </c>
       <c r="H15">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I15">
         <v>100</v>
       </c>
       <c r="J15">
-        <v>110</v>
+        <v>97.8</v>
       </c>
       <c r="K15">
         <v>100</v>
       </c>
       <c r="L15">
-        <v>97.09999999999999</v>
+        <v>92.3</v>
       </c>
       <c r="M15">
-        <v>105</v>
+        <v>97.7</v>
       </c>
       <c r="N15">
         <v>100</v>
       </c>
       <c r="O15">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>97.8</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>92.3</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>97.7</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -3887,7 +3887,7 @@
         <v>80</v>
       </c>
       <c r="C16">
-        <v>115</v>
+        <v>95.8</v>
       </c>
       <c r="D16">
         <v>93.3</v>
@@ -3896,55 +3896,55 @@
         <v>66.7</v>
       </c>
       <c r="F16">
-        <v>90</v>
+        <v>81.8</v>
       </c>
       <c r="G16">
         <v>85</v>
       </c>
       <c r="H16">
-        <v>93.3</v>
+        <v>77.8</v>
       </c>
       <c r="I16">
-        <v>75</v>
+        <v>77.5</v>
       </c>
       <c r="J16">
-        <v>100</v>
+        <v>93.5</v>
       </c>
       <c r="K16">
-        <v>86.7</v>
+        <v>90</v>
       </c>
       <c r="L16">
-        <v>82.90000000000001</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="M16">
-        <v>105</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="N16">
-        <v>80</v>
+        <v>82.5</v>
       </c>
       <c r="O16">
-        <v>120</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>77.5</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>93.5</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>82.5</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>88.90000000000001</v>
       </c>
     </row>
     <row r="17" spans="1:22">
@@ -3955,7 +3955,7 @@
         <v>100</v>
       </c>
       <c r="C17">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="D17">
         <v>100</v>
@@ -3964,55 +3964,55 @@
         <v>100</v>
       </c>
       <c r="F17">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="G17">
         <v>100</v>
       </c>
       <c r="H17">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I17">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="J17">
-        <v>100</v>
+        <v>95.7</v>
       </c>
       <c r="K17">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="L17">
         <v>100</v>
       </c>
       <c r="M17">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="N17">
+        <v>97.5</v>
+      </c>
+      <c r="O17">
+        <v>100</v>
+      </c>
+      <c r="P17">
         <v>95</v>
       </c>
-      <c r="O17">
-        <v>120</v>
-      </c>
-      <c r="P17">
-        <v>0</v>
-      </c>
       <c r="Q17">
-        <v>0</v>
+        <v>95.7</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>95.5</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="18" spans="1:22">
@@ -4053,7 +4053,7 @@
         <v>0</v>
       </c>
       <c r="O18">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="P18">
         <v>0</v>
@@ -4071,7 +4071,7 @@
         <v>0</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19" spans="1:22">
@@ -4082,7 +4082,7 @@
         <v>100</v>
       </c>
       <c r="C19">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="D19">
         <v>93.3</v>
@@ -4091,55 +4091,55 @@
         <v>93.3</v>
       </c>
       <c r="F19">
-        <v>105</v>
+        <v>95.5</v>
       </c>
       <c r="G19">
         <v>95</v>
       </c>
       <c r="H19">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I19">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="J19">
-        <v>105</v>
+        <v>97.8</v>
       </c>
       <c r="K19">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="L19">
-        <v>94.3</v>
+        <v>93.8</v>
       </c>
       <c r="M19">
-        <v>105</v>
+        <v>95.5</v>
       </c>
       <c r="N19">
-        <v>90</v>
+        <v>92.5</v>
       </c>
       <c r="O19">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>97.8</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>93.8</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>95.5</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>92.5</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="20" spans="1:22">
@@ -4150,7 +4150,7 @@
         <v>70</v>
       </c>
       <c r="C20">
-        <v>115</v>
+        <v>95.8</v>
       </c>
       <c r="D20">
         <v>73.3</v>
@@ -4159,55 +4159,55 @@
         <v>83.3</v>
       </c>
       <c r="F20">
-        <v>75</v>
+        <v>68.2</v>
       </c>
       <c r="G20">
         <v>75</v>
       </c>
       <c r="H20">
-        <v>26.7</v>
+        <v>22.2</v>
       </c>
       <c r="I20">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="J20">
-        <v>75</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="K20">
-        <v>86.7</v>
+        <v>80</v>
       </c>
       <c r="L20">
-        <v>54.3</v>
+        <v>67.7</v>
       </c>
       <c r="M20">
+        <v>70.5</v>
+      </c>
+      <c r="N20">
+        <v>65</v>
+      </c>
+      <c r="O20">
+        <v>61.1</v>
+      </c>
+      <c r="P20">
+        <v>45</v>
+      </c>
+      <c r="Q20">
+        <v>82.59999999999999</v>
+      </c>
+      <c r="R20">
         <v>80</v>
       </c>
-      <c r="N20">
-        <v>55</v>
-      </c>
-      <c r="O20">
-        <v>120</v>
-      </c>
-      <c r="P20">
-        <v>0</v>
-      </c>
-      <c r="Q20">
-        <v>0</v>
-      </c>
-      <c r="R20">
-        <v>0</v>
-      </c>
       <c r="S20">
-        <v>0</v>
+        <v>67.7</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>70.5</v>
       </c>
       <c r="U20">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="V20">
-        <v>0</v>
+        <v>61.1</v>
       </c>
     </row>
     <row r="21" spans="1:22">
@@ -4218,7 +4218,7 @@
         <v>70</v>
       </c>
       <c r="C21">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="D21">
         <v>83.3</v>
@@ -4227,55 +4227,55 @@
         <v>86.7</v>
       </c>
       <c r="F21">
-        <v>75</v>
+        <v>68.2</v>
       </c>
       <c r="G21">
         <v>90</v>
       </c>
       <c r="H21">
-        <v>33.3</v>
+        <v>27.8</v>
       </c>
       <c r="I21">
-        <v>75</v>
+        <v>72.5</v>
       </c>
       <c r="J21">
-        <v>75</v>
+        <v>84.8</v>
       </c>
       <c r="K21">
-        <v>73.3</v>
+        <v>78.3</v>
       </c>
       <c r="L21">
-        <v>57.1</v>
+        <v>70.8</v>
       </c>
       <c r="M21">
-        <v>80</v>
+        <v>70.5</v>
       </c>
       <c r="N21">
-        <v>55</v>
+        <v>72.5</v>
       </c>
       <c r="O21">
-        <v>120</v>
+        <v>63.9</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>72.5</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>84.8</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>78.3</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>70.8</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>70.5</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>72.5</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>63.9</v>
       </c>
     </row>
     <row r="22" spans="1:22">
@@ -4286,7 +4286,7 @@
         <v>70</v>
       </c>
       <c r="C22">
-        <v>115</v>
+        <v>95.8</v>
       </c>
       <c r="D22">
         <v>73.3</v>
@@ -4295,55 +4295,55 @@
         <v>66.7</v>
       </c>
       <c r="F22">
-        <v>75</v>
+        <v>68.2</v>
       </c>
       <c r="G22">
         <v>75</v>
       </c>
       <c r="H22">
-        <v>33.3</v>
+        <v>27.8</v>
       </c>
       <c r="I22">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="J22">
-        <v>75</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="K22">
-        <v>80</v>
+        <v>76.7</v>
       </c>
       <c r="L22">
-        <v>65.7</v>
+        <v>66.2</v>
       </c>
       <c r="M22">
-        <v>75</v>
+        <v>68.2</v>
       </c>
       <c r="N22">
-        <v>50</v>
+        <v>62.5</v>
       </c>
       <c r="O22">
-        <v>120</v>
+        <v>63.9</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>76.7</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>66.2</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>68.2</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>62.5</v>
       </c>
       <c r="V22">
-        <v>0</v>
+        <v>63.9</v>
       </c>
     </row>
     <row r="23" spans="1:22">
@@ -4354,7 +4354,7 @@
         <v>70</v>
       </c>
       <c r="C23">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="D23">
         <v>86.7</v>
@@ -4363,55 +4363,55 @@
         <v>76.7</v>
       </c>
       <c r="F23">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="G23">
         <v>85</v>
       </c>
       <c r="H23">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I23">
-        <v>15</v>
+        <v>42.5</v>
       </c>
       <c r="J23">
-        <v>100</v>
+        <v>95.7</v>
       </c>
       <c r="K23">
-        <v>73.3</v>
+        <v>80</v>
       </c>
       <c r="L23">
-        <v>68.59999999999999</v>
+        <v>72.3</v>
       </c>
       <c r="M23">
-        <v>75</v>
+        <v>79.5</v>
       </c>
       <c r="N23">
         <v>85</v>
       </c>
       <c r="O23">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>42.5</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>95.7</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>72.3</v>
       </c>
       <c r="T23">
-        <v>0</v>
+        <v>79.5</v>
       </c>
       <c r="U23">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="V23">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="24" spans="1:22">
@@ -4422,7 +4422,7 @@
         <v>70</v>
       </c>
       <c r="C24">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="D24">
         <v>93.3</v>
@@ -4431,55 +4431,55 @@
         <v>66.7</v>
       </c>
       <c r="F24">
-        <v>95</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="G24">
         <v>85</v>
       </c>
       <c r="H24">
-        <v>86.7</v>
+        <v>72.2</v>
       </c>
       <c r="I24">
+        <v>80</v>
+      </c>
+      <c r="J24">
+        <v>100</v>
+      </c>
+      <c r="K24">
         <v>90</v>
       </c>
-      <c r="J24">
-        <v>110</v>
-      </c>
-      <c r="K24">
-        <v>86.7</v>
-      </c>
       <c r="L24">
+        <v>78.5</v>
+      </c>
+      <c r="M24">
         <v>88.59999999999999</v>
       </c>
-      <c r="M24">
-        <v>100</v>
-      </c>
       <c r="N24">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="O24">
-        <v>120</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>78.5</v>
       </c>
       <c r="T24">
-        <v>0</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="V24">
-        <v>0</v>
+        <v>86.09999999999999</v>
       </c>
     </row>
     <row r="25" spans="1:22">
@@ -4490,7 +4490,7 @@
         <v>90</v>
       </c>
       <c r="C25">
-        <v>115</v>
+        <v>95.8</v>
       </c>
       <c r="D25">
         <v>86.7</v>
@@ -4499,55 +4499,55 @@
         <v>93.3</v>
       </c>
       <c r="F25">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="G25">
         <v>90</v>
       </c>
       <c r="H25">
-        <v>106.7</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="I25">
         <v>90</v>
       </c>
       <c r="J25">
-        <v>105</v>
+        <v>95.7</v>
       </c>
       <c r="K25">
-        <v>93.3</v>
+        <v>90</v>
       </c>
       <c r="L25">
-        <v>85.7</v>
+        <v>89.2</v>
       </c>
       <c r="M25">
-        <v>105</v>
+        <v>93.2</v>
       </c>
       <c r="N25">
-        <v>85</v>
+        <v>87.5</v>
       </c>
       <c r="O25">
-        <v>120</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="Q25">
-        <v>0</v>
+        <v>95.7</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>89.2</v>
       </c>
       <c r="T25">
-        <v>0</v>
+        <v>93.2</v>
       </c>
       <c r="U25">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="V25">
-        <v>0</v>
+        <v>94.40000000000001</v>
       </c>
     </row>
     <row r="26" spans="1:22">
@@ -4558,7 +4558,7 @@
         <v>80</v>
       </c>
       <c r="C26">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="D26">
         <v>100</v>
@@ -4567,55 +4567,55 @@
         <v>90</v>
       </c>
       <c r="F26">
-        <v>105</v>
+        <v>95.5</v>
       </c>
       <c r="G26">
         <v>100</v>
       </c>
       <c r="H26">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I26">
-        <v>95</v>
+        <v>87.5</v>
       </c>
       <c r="J26">
-        <v>105</v>
+        <v>97.8</v>
       </c>
       <c r="K26">
         <v>100</v>
       </c>
       <c r="L26">
-        <v>100</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="M26">
-        <v>110</v>
+        <v>97.7</v>
       </c>
       <c r="N26">
         <v>100</v>
       </c>
       <c r="O26">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>97.8</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="T26">
-        <v>0</v>
+        <v>97.7</v>
       </c>
       <c r="U26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V26">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="27" spans="1:22">
@@ -4626,7 +4626,7 @@
         <v>95</v>
       </c>
       <c r="C27">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="D27">
         <v>100</v>
@@ -4635,55 +4635,55 @@
         <v>100</v>
       </c>
       <c r="F27">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="G27">
         <v>100</v>
       </c>
       <c r="H27">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I27">
-        <v>80</v>
+        <v>87.5</v>
       </c>
       <c r="J27">
-        <v>105</v>
+        <v>97.8</v>
       </c>
       <c r="K27">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="L27">
-        <v>94.3</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="M27">
-        <v>105</v>
+        <v>93.2</v>
       </c>
       <c r="N27">
         <v>100</v>
       </c>
       <c r="O27">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>97.8</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="T27">
-        <v>0</v>
+        <v>93.2</v>
       </c>
       <c r="U27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V27">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="28" spans="1:22">
@@ -4694,7 +4694,7 @@
         <v>70</v>
       </c>
       <c r="C28">
-        <v>115</v>
+        <v>95.8</v>
       </c>
       <c r="D28">
         <v>80</v>
@@ -4703,55 +4703,55 @@
         <v>66.7</v>
       </c>
       <c r="F28">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="G28">
         <v>85</v>
       </c>
       <c r="H28">
+        <v>72.2</v>
+      </c>
+      <c r="I28">
+        <v>57.5</v>
+      </c>
+      <c r="J28">
+        <v>82.59999999999999</v>
+      </c>
+      <c r="K28">
         <v>86.7</v>
       </c>
-      <c r="I28">
-        <v>45</v>
-      </c>
-      <c r="J28">
-        <v>75</v>
-      </c>
-      <c r="K28">
-        <v>93.3</v>
-      </c>
       <c r="L28">
-        <v>54.3</v>
+        <v>60</v>
       </c>
       <c r="M28">
-        <v>90</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="N28">
-        <v>80</v>
+        <v>82.5</v>
       </c>
       <c r="O28">
-        <v>120</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>57.5</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>86.7</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="T28">
-        <v>0</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="U28">
-        <v>0</v>
+        <v>82.5</v>
       </c>
       <c r="V28">
-        <v>0</v>
+        <v>86.09999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/4APV - Estadisticos 20222.xlsx
+++ b/grupos/4APV - Estadisticos 20222.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="70">
   <si>
     <t>Materia</t>
   </si>
@@ -173,24 +173,24 @@
     <t>Villanueva Morales Luis Arturo</t>
   </si>
   <si>
+    <t>González Nuñez Veronica</t>
+  </si>
+  <si>
     <t>Polanco Domínguez Rosa María</t>
   </si>
   <si>
-    <t>González Nuñez Veronica</t>
-  </si>
-  <si>
     <t>Rodriguez Roman Marisol</t>
   </si>
   <si>
+    <t>De Jesús Orduña Sofía del Pilar</t>
+  </si>
+  <si>
     <t>Muñoz Rivadeneyra Salvador</t>
   </si>
   <si>
     <t>Acevedo Rendón Ismael Arturo</t>
   </si>
   <si>
-    <t>De Jesús Orduña Sofía del Pilar</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -203,13 +203,16 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
     <t>TRUJILLO</t>
   </si>
   <si>
     <t>CERON</t>
   </si>
   <si>
-    <t>FLORES</t>
+    <t>GARCIA</t>
   </si>
   <si>
     <t>CASTRO</t>
@@ -218,16 +221,13 @@
     <t>TZOMPAXTLE</t>
   </si>
   <si>
-    <t>VILLA</t>
+    <t>CLAUDIA</t>
   </si>
   <si>
     <t>MARIA DEL CARMEN</t>
   </si>
   <si>
     <t>MARIA JOSE</t>
-  </si>
-  <si>
-    <t>DIEGO</t>
   </si>
 </sst>
 </file>
@@ -775,22 +775,22 @@
         <v>10</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T4">
         <v>-1</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V4">
         <v>-1</v>
@@ -864,22 +864,22 @@
         <v>5</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T5">
         <v>-1</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V5">
         <v>-1</v>
@@ -888,7 +888,7 @@
         <v>6</v>
       </c>
       <c r="X5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y5">
         <v>7</v>
@@ -953,28 +953,28 @@
         <v>5</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T6">
         <v>-1</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V6">
         <v>-1</v>
       </c>
       <c r="W6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X6">
         <v>5</v>
@@ -1042,34 +1042,34 @@
         <v>5</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T7">
         <v>-1</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V7">
         <v>-1</v>
       </c>
       <c r="W7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z7">
         <v>9</v>
@@ -1078,7 +1078,7 @@
         <v>5</v>
       </c>
       <c r="AB7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC7">
         <v>7</v>
@@ -1131,22 +1131,22 @@
         <v>6</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T8">
         <v>-1</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V8">
         <v>-1</v>
@@ -1161,7 +1161,7 @@
         <v>5</v>
       </c>
       <c r="Z8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA8">
         <v>5</v>
@@ -1220,22 +1220,22 @@
         <v>10</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T9">
         <v>-1</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V9">
         <v>-1</v>
@@ -1309,22 +1309,22 @@
         <v>5</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T10">
         <v>-1</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V10">
         <v>-1</v>
@@ -1333,10 +1333,10 @@
         <v>5</v>
       </c>
       <c r="X10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z10">
         <v>5</v>
@@ -1398,28 +1398,28 @@
         <v>8</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T11">
         <v>-1</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V11">
         <v>-1</v>
       </c>
       <c r="W11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X11">
         <v>7</v>
@@ -1434,7 +1434,7 @@
         <v>9</v>
       </c>
       <c r="AB11">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AC11">
         <v>8</v>
@@ -1487,22 +1487,22 @@
         <v>5</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T12">
         <v>-1</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V12">
         <v>-1</v>
@@ -1517,13 +1517,13 @@
         <v>5</v>
       </c>
       <c r="Z12">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AA12">
         <v>5</v>
       </c>
       <c r="AB12">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AC12">
         <v>5</v>
@@ -1576,34 +1576,34 @@
         <v>7</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T13">
         <v>-1</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V13">
         <v>-1</v>
       </c>
       <c r="W13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z13">
         <v>9</v>
@@ -1612,7 +1612,7 @@
         <v>9</v>
       </c>
       <c r="AB13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC13">
         <v>8</v>
@@ -1665,22 +1665,22 @@
         <v>6</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T14">
         <v>-1</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V14">
         <v>-1</v>
@@ -1689,10 +1689,10 @@
         <v>5</v>
       </c>
       <c r="X14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z14">
         <v>5</v>
@@ -1754,22 +1754,22 @@
         <v>10</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T15">
         <v>-1</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V15">
         <v>-1</v>
@@ -1843,31 +1843,31 @@
         <v>5</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T16">
         <v>-1</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V16">
         <v>-1</v>
       </c>
       <c r="W16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y16">
         <v>7</v>
@@ -1932,22 +1932,22 @@
         <v>5</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T17">
         <v>-1</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V17">
         <v>-1</v>
@@ -1959,7 +1959,7 @@
         <v>6</v>
       </c>
       <c r="Y17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z17">
         <v>8</v>
@@ -1968,7 +1968,7 @@
         <v>5</v>
       </c>
       <c r="AB17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC17">
         <v>5</v>
@@ -2015,16 +2015,16 @@
         <v>5</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T18">
         <v>-1</v>
@@ -2098,22 +2098,22 @@
         <v>8</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T19">
         <v>-1</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V19">
         <v>-1</v>
@@ -2128,7 +2128,7 @@
         <v>8</v>
       </c>
       <c r="Z19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA19">
         <v>7</v>
@@ -2187,22 +2187,22 @@
         <v>5</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T20">
         <v>-1</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V20">
         <v>-1</v>
@@ -2276,37 +2276,37 @@
         <v>5</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T21">
         <v>-1</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V21">
         <v>-1</v>
       </c>
       <c r="W21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X21">
         <v>6</v>
       </c>
       <c r="Y21">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Z21">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA21">
         <v>5</v>
@@ -2365,22 +2365,22 @@
         <v>5</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T22">
         <v>-1</v>
       </c>
       <c r="U22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V22">
         <v>-1</v>
@@ -2454,22 +2454,22 @@
         <v>5</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T23">
         <v>-1</v>
       </c>
       <c r="U23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V23">
         <v>-1</v>
@@ -2478,7 +2478,7 @@
         <v>5</v>
       </c>
       <c r="X23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y23">
         <v>5</v>
@@ -2490,7 +2490,7 @@
         <v>5</v>
       </c>
       <c r="AB23">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC23">
         <v>5</v>
@@ -2543,22 +2543,22 @@
         <v>8</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T24">
         <v>-1</v>
       </c>
       <c r="U24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V24">
         <v>-1</v>
@@ -2579,7 +2579,7 @@
         <v>8</v>
       </c>
       <c r="AB24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC24">
         <v>8</v>
@@ -2632,22 +2632,22 @@
         <v>6</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T25">
         <v>-1</v>
       </c>
       <c r="U25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V25">
         <v>-1</v>
@@ -2656,13 +2656,13 @@
         <v>6</v>
       </c>
       <c r="X25">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y25">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z25">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA25">
         <v>5</v>
@@ -2721,22 +2721,22 @@
         <v>7</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T26">
         <v>-1</v>
       </c>
       <c r="U26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V26">
         <v>-1</v>
@@ -2810,22 +2810,22 @@
         <v>8</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T27">
         <v>-1</v>
       </c>
       <c r="U27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V27">
         <v>-1</v>
@@ -2837,16 +2837,16 @@
         <v>6</v>
       </c>
       <c r="Y27">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z27">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA27">
         <v>5</v>
       </c>
       <c r="AB27">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC27">
         <v>8</v>
@@ -2899,22 +2899,22 @@
         <v>5</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T28">
         <v>-1</v>
       </c>
       <c r="U28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V28">
         <v>-1</v>
@@ -3178,22 +3178,22 @@
         <v>88.90000000000001</v>
       </c>
       <c r="P5">
-        <v>90</v>
+        <v>87.5</v>
       </c>
       <c r="Q5">
-        <v>93.5</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="R5">
-        <v>93.3</v>
+        <v>93.8</v>
       </c>
       <c r="S5">
-        <v>86.2</v>
+        <v>83</v>
       </c>
       <c r="T5">
         <v>93.2</v>
       </c>
       <c r="U5">
-        <v>97.5</v>
+        <v>95</v>
       </c>
       <c r="V5">
         <v>88.90000000000001</v>
@@ -3246,22 +3246,22 @@
         <v>83.3</v>
       </c>
       <c r="P6">
-        <v>35</v>
+        <v>21.9</v>
       </c>
       <c r="Q6">
-        <v>82.59999999999999</v>
+        <v>57.6</v>
       </c>
       <c r="R6">
-        <v>73.3</v>
+        <v>45.8</v>
       </c>
       <c r="S6">
-        <v>52.3</v>
+        <v>36.6</v>
       </c>
       <c r="T6">
         <v>68.2</v>
       </c>
       <c r="U6">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="V6">
         <v>83.3</v>
@@ -3314,22 +3314,22 @@
         <v>88.90000000000001</v>
       </c>
       <c r="P7">
-        <v>85</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="Q7">
-        <v>97.8</v>
+        <v>98.5</v>
       </c>
       <c r="R7">
-        <v>96.7</v>
+        <v>95.8</v>
       </c>
       <c r="S7">
-        <v>84.59999999999999</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="T7">
         <v>79.5</v>
       </c>
       <c r="U7">
-        <v>97.5</v>
+        <v>95</v>
       </c>
       <c r="V7">
         <v>88.90000000000001</v>
@@ -3382,22 +3382,22 @@
         <v>91.7</v>
       </c>
       <c r="P8">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="Q8">
-        <v>91.3</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="R8">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="S8">
-        <v>66.2</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="T8">
         <v>75</v>
       </c>
       <c r="U8">
-        <v>77.5</v>
+        <v>73.3</v>
       </c>
       <c r="V8">
         <v>91.7</v>
@@ -3450,7 +3450,7 @@
         <v>100</v>
       </c>
       <c r="P9">
-        <v>87.5</v>
+        <v>92.2</v>
       </c>
       <c r="Q9">
         <v>100</v>
@@ -3459,13 +3459,13 @@
         <v>100</v>
       </c>
       <c r="S9">
-        <v>98.5</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="T9">
         <v>95.5</v>
       </c>
       <c r="U9">
-        <v>97.5</v>
+        <v>98.3</v>
       </c>
       <c r="V9">
         <v>100</v>
@@ -3518,22 +3518,22 @@
         <v>100</v>
       </c>
       <c r="P10">
-        <v>42.5</v>
+        <v>32.8</v>
       </c>
       <c r="Q10">
-        <v>97.8</v>
+        <v>97</v>
       </c>
       <c r="R10">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="S10">
-        <v>75.40000000000001</v>
+        <v>70.5</v>
       </c>
       <c r="T10">
         <v>79.5</v>
       </c>
       <c r="U10">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="V10">
         <v>100</v>
@@ -3592,10 +3592,10 @@
         <v>100</v>
       </c>
       <c r="R11">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="S11">
-        <v>100</v>
+        <v>97.3</v>
       </c>
       <c r="T11">
         <v>97.7</v>
@@ -3654,22 +3654,22 @@
         <v>88.90000000000001</v>
       </c>
       <c r="P12">
-        <v>85</v>
+        <v>53.1</v>
       </c>
       <c r="Q12">
-        <v>95.7</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="R12">
-        <v>80</v>
+        <v>60.4</v>
       </c>
       <c r="S12">
-        <v>76.90000000000001</v>
+        <v>53.6</v>
       </c>
       <c r="T12">
         <v>77.3</v>
       </c>
       <c r="U12">
-        <v>80</v>
+        <v>53.3</v>
       </c>
       <c r="V12">
         <v>88.90000000000001</v>
@@ -3725,19 +3725,19 @@
         <v>100</v>
       </c>
       <c r="Q13">
-        <v>100</v>
+        <v>98.5</v>
       </c>
       <c r="R13">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="S13">
-        <v>100</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="T13">
         <v>93.2</v>
       </c>
       <c r="U13">
-        <v>90</v>
+        <v>91.7</v>
       </c>
       <c r="V13">
         <v>100</v>
@@ -3790,16 +3790,16 @@
         <v>88.90000000000001</v>
       </c>
       <c r="P14">
-        <v>42.5</v>
+        <v>35.9</v>
       </c>
       <c r="Q14">
-        <v>82.59999999999999</v>
+        <v>84.8</v>
       </c>
       <c r="R14">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="S14">
-        <v>66.2</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="T14">
         <v>77.3</v>
@@ -3861,13 +3861,13 @@
         <v>100</v>
       </c>
       <c r="Q15">
-        <v>97.8</v>
+        <v>97</v>
       </c>
       <c r="R15">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="S15">
-        <v>92.3</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="T15">
         <v>97.7</v>
@@ -3926,22 +3926,22 @@
         <v>88.90000000000001</v>
       </c>
       <c r="P16">
-        <v>77.5</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="Q16">
-        <v>93.5</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="R16">
-        <v>90</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="S16">
-        <v>75.40000000000001</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="T16">
         <v>88.59999999999999</v>
       </c>
       <c r="U16">
-        <v>82.5</v>
+        <v>78.3</v>
       </c>
       <c r="V16">
         <v>88.90000000000001</v>
@@ -3994,22 +3994,22 @@
         <v>100</v>
       </c>
       <c r="P17">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q17">
-        <v>95.7</v>
+        <v>95.5</v>
       </c>
       <c r="R17">
-        <v>96.7</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S17">
-        <v>100</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="T17">
         <v>95.5</v>
       </c>
       <c r="U17">
-        <v>97.5</v>
+        <v>91.7</v>
       </c>
       <c r="V17">
         <v>100</v>
@@ -4121,13 +4121,13 @@
         <v>100</v>
       </c>
       <c r="P19">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q19">
-        <v>97.8</v>
+        <v>97</v>
       </c>
       <c r="R19">
-        <v>96.7</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S19">
         <v>93.8</v>
@@ -4136,7 +4136,7 @@
         <v>95.5</v>
       </c>
       <c r="U19">
-        <v>92.5</v>
+        <v>91.7</v>
       </c>
       <c r="V19">
         <v>100</v>
@@ -4189,22 +4189,22 @@
         <v>61.1</v>
       </c>
       <c r="P20">
-        <v>45</v>
+        <v>34.4</v>
       </c>
       <c r="Q20">
-        <v>82.59999999999999</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="R20">
-        <v>80</v>
+        <v>79.2</v>
       </c>
       <c r="S20">
-        <v>67.7</v>
+        <v>75</v>
       </c>
       <c r="T20">
         <v>70.5</v>
       </c>
       <c r="U20">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="V20">
         <v>61.1</v>
@@ -4257,22 +4257,22 @@
         <v>63.9</v>
       </c>
       <c r="P21">
-        <v>72.5</v>
+        <v>82.8</v>
       </c>
       <c r="Q21">
-        <v>84.8</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="R21">
-        <v>78.3</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="S21">
-        <v>70.8</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="T21">
         <v>70.5</v>
       </c>
       <c r="U21">
-        <v>72.5</v>
+        <v>78.3</v>
       </c>
       <c r="V21">
         <v>63.9</v>
@@ -4325,22 +4325,22 @@
         <v>63.9</v>
       </c>
       <c r="P22">
-        <v>55</v>
+        <v>40.6</v>
       </c>
       <c r="Q22">
-        <v>82.59999999999999</v>
+        <v>84.8</v>
       </c>
       <c r="R22">
-        <v>76.7</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="S22">
-        <v>66.2</v>
+        <v>72.3</v>
       </c>
       <c r="T22">
         <v>68.2</v>
       </c>
       <c r="U22">
-        <v>62.5</v>
+        <v>66.7</v>
       </c>
       <c r="V22">
         <v>63.9</v>
@@ -4393,22 +4393,22 @@
         <v>100</v>
       </c>
       <c r="P23">
-        <v>42.5</v>
+        <v>32.8</v>
       </c>
       <c r="Q23">
-        <v>95.7</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="R23">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="S23">
-        <v>72.3</v>
+        <v>68.8</v>
       </c>
       <c r="T23">
         <v>79.5</v>
       </c>
       <c r="U23">
-        <v>85</v>
+        <v>81.7</v>
       </c>
       <c r="V23">
         <v>100</v>
@@ -4461,22 +4461,22 @@
         <v>86.09999999999999</v>
       </c>
       <c r="P24">
-        <v>80</v>
+        <v>87.5</v>
       </c>
       <c r="Q24">
         <v>100</v>
       </c>
       <c r="R24">
-        <v>90</v>
+        <v>91.7</v>
       </c>
       <c r="S24">
-        <v>78.5</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="T24">
         <v>88.59999999999999</v>
       </c>
       <c r="U24">
-        <v>90</v>
+        <v>93.3</v>
       </c>
       <c r="V24">
         <v>86.09999999999999</v>
@@ -4529,22 +4529,22 @@
         <v>94.40000000000001</v>
       </c>
       <c r="P25">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="Q25">
-        <v>95.7</v>
+        <v>95.5</v>
       </c>
       <c r="R25">
-        <v>90</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="S25">
-        <v>89.2</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="T25">
         <v>93.2</v>
       </c>
       <c r="U25">
-        <v>87.5</v>
+        <v>85</v>
       </c>
       <c r="V25">
         <v>94.40000000000001</v>
@@ -4597,16 +4597,16 @@
         <v>100</v>
       </c>
       <c r="P26">
-        <v>87.5</v>
+        <v>92.2</v>
       </c>
       <c r="Q26">
-        <v>97.8</v>
+        <v>98.5</v>
       </c>
       <c r="R26">
         <v>100</v>
       </c>
       <c r="S26">
-        <v>95.40000000000001</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="T26">
         <v>97.7</v>
@@ -4665,22 +4665,22 @@
         <v>100</v>
       </c>
       <c r="P27">
-        <v>87.5</v>
+        <v>70.3</v>
       </c>
       <c r="Q27">
-        <v>97.8</v>
+        <v>97</v>
       </c>
       <c r="R27">
-        <v>96.7</v>
+        <v>86.5</v>
       </c>
       <c r="S27">
-        <v>96.90000000000001</v>
+        <v>83</v>
       </c>
       <c r="T27">
         <v>93.2</v>
       </c>
       <c r="U27">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="V27">
         <v>100</v>
@@ -4733,22 +4733,22 @@
         <v>86.09999999999999</v>
       </c>
       <c r="P28">
-        <v>57.5</v>
+        <v>45.3</v>
       </c>
       <c r="Q28">
-        <v>82.59999999999999</v>
+        <v>72.7</v>
       </c>
       <c r="R28">
-        <v>86.7</v>
+        <v>86.5</v>
       </c>
       <c r="S28">
-        <v>60</v>
+        <v>48.2</v>
       </c>
       <c r="T28">
         <v>86.40000000000001</v>
       </c>
       <c r="U28">
-        <v>82.5</v>
+        <v>76.7</v>
       </c>
       <c r="V28">
         <v>86.09999999999999</v>
@@ -4840,28 +4840,28 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3" t="s">
         <v>51</v>
       </c>
       <c r="C3">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E3">
         <v>12</v>
       </c>
       <c r="F3" s="2">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G3" s="2">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="H3">
-        <v>6.1</v>
+        <v>6.5</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -4872,28 +4872,28 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
         <v>52</v>
       </c>
       <c r="C4">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D4">
         <v>13</v>
       </c>
       <c r="E4">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F4" s="2">
-        <v>52</v>
+        <v>54.2</v>
       </c>
       <c r="G4" s="2">
-        <v>48</v>
+        <v>45.8</v>
       </c>
       <c r="H4">
-        <v>6.5</v>
+        <v>6.1</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -4913,19 +4913,19 @@
         <v>25</v>
       </c>
       <c r="D5">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E5">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F5" s="2">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="G5" s="2">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H5">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4936,7 +4936,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
         <v>54</v>
@@ -4945,19 +4945,19 @@
         <v>25</v>
       </c>
       <c r="D6">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E6">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F6" s="2">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="G6" s="2">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="H6">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4968,7 +4968,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
         <v>55</v>
@@ -4977,19 +4977,19 @@
         <v>25</v>
       </c>
       <c r="D7">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E7">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F7" s="2">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="G7" s="2">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="H7">
-        <v>7.3</v>
+        <v>6.2</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -5000,7 +5000,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B8" t="s">
         <v>56</v>
@@ -5009,19 +5009,19 @@
         <v>25</v>
       </c>
       <c r="D8">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E8">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F8" s="2">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="G8" s="2">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="H8">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -5071,7 +5071,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5103,7 +5103,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920152</v>
+        <v>21330051920122</v>
       </c>
       <c r="B2" t="s">
         <v>61</v>
@@ -5115,10 +5115,10 @@
         <v>67</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -5126,7 +5126,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920152</v>
+        <v>21330051920122</v>
       </c>
       <c r="B3" t="s">
         <v>61</v>
@@ -5138,10 +5138,10 @@
         <v>67</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -5149,7 +5149,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920114</v>
+        <v>20330051920152</v>
       </c>
       <c r="B4" t="s">
         <v>62</v>
@@ -5161,10 +5161,10 @@
         <v>68</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -5172,24 +5172,47 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920118</v>
+        <v>20330051920152</v>
       </c>
       <c r="B5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C5" t="s">
+        <v>65</v>
+      </c>
+      <c r="D5" t="s">
+        <v>68</v>
+      </c>
+      <c r="E5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" t="s">
+        <v>50</v>
+      </c>
+      <c r="G5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>21330051920114</v>
+      </c>
+      <c r="B6" t="s">
         <v>63</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C6" t="s">
         <v>66</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D6" t="s">
         <v>69</v>
       </c>
-      <c r="E5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" t="s">
-        <v>51</v>
-      </c>
-      <c r="G5">
+      <c r="E6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" t="s">
+        <v>50</v>
+      </c>
+      <c r="G6">
         <v>5</v>
       </c>
     </row>

--- a/grupos/4APV - Estadisticos 20222.xlsx
+++ b/grupos/4APV - Estadisticos 20222.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="76">
   <si>
     <t>Materia</t>
   </si>
@@ -173,24 +173,24 @@
     <t>Villanueva Morales Luis Arturo</t>
   </si>
   <si>
+    <t>Polanco Domínguez Rosa María</t>
+  </si>
+  <si>
+    <t>Rodriguez Roman Marisol</t>
+  </si>
+  <si>
+    <t>De Jesús Orduña Sofía del Pilar</t>
+  </si>
+  <si>
+    <t>Muñoz Rivadeneyra Salvador</t>
+  </si>
+  <si>
+    <t>Acevedo Rendón Ismael Arturo</t>
+  </si>
+  <si>
     <t>González Nuñez Veronica</t>
   </si>
   <si>
-    <t>Polanco Domínguez Rosa María</t>
-  </si>
-  <si>
-    <t>Rodriguez Roman Marisol</t>
-  </si>
-  <si>
-    <t>De Jesús Orduña Sofía del Pilar</t>
-  </si>
-  <si>
-    <t>Muñoz Rivadeneyra Salvador</t>
-  </si>
-  <si>
-    <t>Acevedo Rendón Ismael Arturo</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -203,31 +203,49 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>BARRAGAN</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>CERON</t>
+  </si>
+  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>CERON</t>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>CAPORAL</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>TZOMPAXTLE</t>
   </si>
   <si>
     <t>GARCIA</t>
   </si>
   <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>TZOMPAXTLE</t>
+    <t>KAREN ITZEL</t>
+  </si>
+  <si>
+    <t>LOGAN FRANCISCO</t>
+  </si>
+  <si>
+    <t>MARIA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>MARIA JOSE</t>
   </si>
   <si>
     <t>CLAUDIA</t>
-  </si>
-  <si>
-    <t>MARIA DEL CARMEN</t>
-  </si>
-  <si>
-    <t>MARIA JOSE</t>
   </si>
 </sst>
 </file>
@@ -793,7 +811,7 @@
         <v>10</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W4">
         <v>9</v>
@@ -882,7 +900,7 @@
         <v>5</v>
       </c>
       <c r="V5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W5">
         <v>6</v>
@@ -903,7 +921,7 @@
         <v>5</v>
       </c>
       <c r="AC5">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:29">
@@ -971,7 +989,7 @@
         <v>5</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W6">
         <v>5</v>
@@ -1060,7 +1078,7 @@
         <v>6</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W7">
         <v>7</v>
@@ -1149,7 +1167,7 @@
         <v>5</v>
       </c>
       <c r="V8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W8">
         <v>5</v>
@@ -1170,7 +1188,7 @@
         <v>5</v>
       </c>
       <c r="AC8">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:29">
@@ -1238,7 +1256,7 @@
         <v>10</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W9">
         <v>10</v>
@@ -1327,7 +1345,7 @@
         <v>6</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W10">
         <v>5</v>
@@ -1348,7 +1366,7 @@
         <v>6</v>
       </c>
       <c r="AC10">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:29">
@@ -1416,7 +1434,7 @@
         <v>10</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W11">
         <v>9</v>
@@ -1505,7 +1523,7 @@
         <v>5</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="W12">
         <v>5</v>
@@ -1594,7 +1612,7 @@
         <v>10</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W13">
         <v>9</v>
@@ -1683,7 +1701,7 @@
         <v>5</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W14">
         <v>5</v>
@@ -1704,7 +1722,7 @@
         <v>5</v>
       </c>
       <c r="AC14">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:29">
@@ -1772,7 +1790,7 @@
         <v>6</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W15">
         <v>8</v>
@@ -1861,7 +1879,7 @@
         <v>5</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W16">
         <v>8</v>
@@ -1882,7 +1900,7 @@
         <v>5</v>
       </c>
       <c r="AC16">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:29">
@@ -1950,7 +1968,7 @@
         <v>7</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W17">
         <v>8</v>
@@ -1971,7 +1989,7 @@
         <v>6</v>
       </c>
       <c r="AC17">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:29">
@@ -2030,7 +2048,7 @@
         <v>-1</v>
       </c>
       <c r="V18">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="W18">
         <v>5</v>
@@ -2116,7 +2134,7 @@
         <v>7</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W19">
         <v>9</v>
@@ -2205,7 +2223,7 @@
         <v>5</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W20">
         <v>5</v>
@@ -2294,7 +2312,7 @@
         <v>7</v>
       </c>
       <c r="V21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W21">
         <v>8</v>
@@ -2383,7 +2401,7 @@
         <v>5</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W22">
         <v>5</v>
@@ -2472,7 +2490,7 @@
         <v>6</v>
       </c>
       <c r="V23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W23">
         <v>5</v>
@@ -2493,7 +2511,7 @@
         <v>6</v>
       </c>
       <c r="AC23">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24" spans="1:29">
@@ -2561,7 +2579,7 @@
         <v>10</v>
       </c>
       <c r="V24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W24">
         <v>8</v>
@@ -2650,7 +2668,7 @@
         <v>5</v>
       </c>
       <c r="V25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W25">
         <v>6</v>
@@ -2739,7 +2757,7 @@
         <v>9</v>
       </c>
       <c r="V26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W26">
         <v>9</v>
@@ -2828,7 +2846,7 @@
         <v>5</v>
       </c>
       <c r="V27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W27">
         <v>5</v>
@@ -2917,7 +2935,7 @@
         <v>5</v>
       </c>
       <c r="V28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W28">
         <v>5</v>
@@ -2938,7 +2956,7 @@
         <v>5</v>
       </c>
       <c r="AC28">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -3196,7 +3214,7 @@
         <v>95</v>
       </c>
       <c r="V5">
-        <v>88.90000000000001</v>
+        <v>92.59999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:22">
@@ -3264,7 +3282,7 @@
         <v>30</v>
       </c>
       <c r="V6">
-        <v>83.3</v>
+        <v>88.90000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -3332,7 +3350,7 @@
         <v>95</v>
       </c>
       <c r="V7">
-        <v>88.90000000000001</v>
+        <v>92.59999999999999</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -3400,7 +3418,7 @@
         <v>73.3</v>
       </c>
       <c r="V8">
-        <v>91.7</v>
+        <v>94.40000000000001</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -3672,7 +3690,7 @@
         <v>53.3</v>
       </c>
       <c r="V12">
-        <v>88.90000000000001</v>
+        <v>59.3</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -3808,7 +3826,7 @@
         <v>85</v>
       </c>
       <c r="V14">
-        <v>88.90000000000001</v>
+        <v>92.59999999999999</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -3944,7 +3962,7 @@
         <v>78.3</v>
       </c>
       <c r="V16">
-        <v>88.90000000000001</v>
+        <v>92.59999999999999</v>
       </c>
     </row>
     <row r="17" spans="1:22">
@@ -4071,7 +4089,7 @@
         <v>0</v>
       </c>
       <c r="V18">
-        <v>50</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="19" spans="1:22">
@@ -4207,7 +4225,7 @@
         <v>75</v>
       </c>
       <c r="V20">
-        <v>61.1</v>
+        <v>74.09999999999999</v>
       </c>
     </row>
     <row r="21" spans="1:22">
@@ -4275,7 +4293,7 @@
         <v>78.3</v>
       </c>
       <c r="V21">
-        <v>63.9</v>
+        <v>75.90000000000001</v>
       </c>
     </row>
     <row r="22" spans="1:22">
@@ -4343,7 +4361,7 @@
         <v>66.7</v>
       </c>
       <c r="V22">
-        <v>63.9</v>
+        <v>75.90000000000001</v>
       </c>
     </row>
     <row r="23" spans="1:22">
@@ -4479,7 +4497,7 @@
         <v>93.3</v>
       </c>
       <c r="V24">
-        <v>86.09999999999999</v>
+        <v>90.7</v>
       </c>
     </row>
     <row r="25" spans="1:22">
@@ -4547,7 +4565,7 @@
         <v>85</v>
       </c>
       <c r="V25">
-        <v>94.40000000000001</v>
+        <v>96.3</v>
       </c>
     </row>
     <row r="26" spans="1:22">
@@ -4751,7 +4769,7 @@
         <v>76.7</v>
       </c>
       <c r="V28">
-        <v>86.09999999999999</v>
+        <v>90.7</v>
       </c>
     </row>
   </sheetData>
@@ -4840,28 +4858,28 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
         <v>51</v>
       </c>
       <c r="C3">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D3">
         <v>13</v>
       </c>
       <c r="E3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F3" s="2">
-        <v>52</v>
+        <v>54.2</v>
       </c>
       <c r="G3" s="2">
-        <v>48</v>
+        <v>45.8</v>
       </c>
       <c r="H3">
-        <v>6.5</v>
+        <v>6.1</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -4872,28 +4890,28 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
         <v>52</v>
       </c>
       <c r="C4">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D4">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E4">
         <v>11</v>
       </c>
       <c r="F4" s="2">
-        <v>54.2</v>
+        <v>56</v>
       </c>
       <c r="G4" s="2">
-        <v>45.8</v>
+        <v>44</v>
       </c>
       <c r="H4">
-        <v>6.1</v>
+        <v>6.8</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -4904,7 +4922,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
         <v>53</v>
@@ -4925,7 +4943,7 @@
         <v>44</v>
       </c>
       <c r="H5">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4936,7 +4954,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
         <v>54</v>
@@ -4945,19 +4963,19 @@
         <v>25</v>
       </c>
       <c r="D6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E6">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F6" s="2">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="G6" s="2">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="H6">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4968,7 +4986,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
         <v>55</v>
@@ -4989,7 +5007,7 @@
         <v>40</v>
       </c>
       <c r="H7">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -5000,7 +5018,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B8" t="s">
         <v>56</v>
@@ -5009,19 +5027,19 @@
         <v>25</v>
       </c>
       <c r="D8">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F8" s="2">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="G8" s="2">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="H8">
-        <v>7</v>
+        <v>6.7</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -5071,7 +5089,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5103,16 +5121,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920122</v>
+        <v>21330051920111</v>
       </c>
       <c r="B2" t="s">
         <v>61</v>
       </c>
       <c r="C2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D2" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
@@ -5126,19 +5144,19 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920122</v>
+        <v>21330051920111</v>
       </c>
       <c r="B3" t="s">
         <v>61</v>
       </c>
       <c r="C3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D3" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
         <v>51</v>
@@ -5149,22 +5167,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920152</v>
+        <v>21330051920391</v>
       </c>
       <c r="B4" t="s">
         <v>62</v>
       </c>
       <c r="C4" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D4" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -5172,22 +5190,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920152</v>
+        <v>21330051920391</v>
       </c>
       <c r="B5" t="s">
         <v>62</v>
       </c>
       <c r="C5" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D5" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -5195,24 +5213,93 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920114</v>
+        <v>20330051920152</v>
       </c>
       <c r="B6" t="s">
         <v>63</v>
       </c>
       <c r="C6" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D6" t="s">
+        <v>73</v>
+      </c>
+      <c r="E6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F6" t="s">
+        <v>52</v>
+      </c>
+      <c r="G6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>20330051920152</v>
+      </c>
+      <c r="B7" t="s">
+        <v>63</v>
+      </c>
+      <c r="C7" t="s">
+        <v>68</v>
+      </c>
+      <c r="D7" t="s">
+        <v>73</v>
+      </c>
+      <c r="E7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F7" t="s">
+        <v>50</v>
+      </c>
+      <c r="G7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>21330051920114</v>
+      </c>
+      <c r="B8" t="s">
+        <v>64</v>
+      </c>
+      <c r="C8" t="s">
         <v>69</v>
       </c>
-      <c r="E6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" t="s">
+      <c r="D8" t="s">
+        <v>74</v>
+      </c>
+      <c r="E8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" t="s">
         <v>50</v>
       </c>
-      <c r="G6">
+      <c r="G8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>21330051920122</v>
+      </c>
+      <c r="B9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C9" t="s">
+        <v>70</v>
+      </c>
+      <c r="D9" t="s">
+        <v>75</v>
+      </c>
+      <c r="E9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F9" t="s">
+        <v>50</v>
+      </c>
+      <c r="G9">
         <v>5</v>
       </c>
     </row>

--- a/grupos/4APV - Estadisticos 20222.xlsx
+++ b/grupos/4APV - Estadisticos 20222.xlsx
@@ -179,13 +179,13 @@
     <t>Rodriguez Roman Marisol</t>
   </si>
   <si>
+    <t>Muñoz Rivadeneyra Salvador</t>
+  </si>
+  <si>
+    <t>Acevedo Rendón Ismael Arturo</t>
+  </si>
+  <si>
     <t>De Jesús Orduña Sofía del Pilar</t>
-  </si>
-  <si>
-    <t>Muñoz Rivadeneyra Salvador</t>
-  </si>
-  <si>
-    <t>Acevedo Rendón Ismael Arturo</t>
   </si>
   <si>
     <t>González Nuñez Veronica</t>
@@ -2321,7 +2321,7 @@
         <v>6</v>
       </c>
       <c r="Y21">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z21">
         <v>6</v>
@@ -4281,7 +4281,7 @@
         <v>87.90000000000001</v>
       </c>
       <c r="R21">
-        <v>78.09999999999999</v>
+        <v>86.5</v>
       </c>
       <c r="S21">
         <v>82.09999999999999</v>
@@ -4922,7 +4922,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
         <v>53</v>
@@ -4931,19 +4931,19 @@
         <v>25</v>
       </c>
       <c r="D5">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E5">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F5" s="2">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="G5" s="2">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="H5">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4954,7 +4954,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
         <v>54</v>
@@ -4975,7 +4975,7 @@
         <v>40</v>
       </c>
       <c r="H6">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4986,7 +4986,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B7" t="s">
         <v>55</v>
@@ -5007,7 +5007,7 @@
         <v>40</v>
       </c>
       <c r="H7">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="I7">
         <v>0</v>

--- a/grupos/4APV - Estadisticos 20222.xlsx
+++ b/grupos/4APV - Estadisticos 20222.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="73">
   <si>
     <t>Materia</t>
   </si>
@@ -170,24 +170,24 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Polanco Domínguez Rosa María</t>
+  </si>
+  <si>
+    <t>Rodriguez Roman Marisol</t>
+  </si>
+  <si>
+    <t>Muñoz Rivadeneyra Salvador</t>
+  </si>
+  <si>
+    <t>Acevedo Rendón Ismael Arturo</t>
+  </si>
+  <si>
+    <t>De Jesús Orduña Sofía del Pilar</t>
+  </si>
+  <si>
     <t>Villanueva Morales Luis Arturo</t>
   </si>
   <si>
-    <t>Polanco Domínguez Rosa María</t>
-  </si>
-  <si>
-    <t>Rodriguez Roman Marisol</t>
-  </si>
-  <si>
-    <t>Muñoz Rivadeneyra Salvador</t>
-  </si>
-  <si>
-    <t>Acevedo Rendón Ismael Arturo</t>
-  </si>
-  <si>
-    <t>De Jesús Orduña Sofía del Pilar</t>
-  </si>
-  <si>
     <t>González Nuñez Veronica</t>
   </si>
   <si>
@@ -209,43 +209,34 @@
     <t>GOMEZ</t>
   </si>
   <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
     <t>TRUJILLO</t>
   </si>
   <si>
-    <t>CERON</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
     <t>LOPEZ</t>
   </si>
   <si>
     <t>CAPORAL</t>
   </si>
   <si>
+    <t>FLORES</t>
+  </si>
+  <si>
     <t>CASTRO</t>
   </si>
   <si>
-    <t>TZOMPAXTLE</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
     <t>KAREN ITZEL</t>
   </si>
   <si>
     <t>LOGAN FRANCISCO</t>
   </si>
   <si>
+    <t>ZABDIEL</t>
+  </si>
+  <si>
     <t>MARIA DEL CARMEN</t>
-  </si>
-  <si>
-    <t>MARIA JOSE</t>
-  </si>
-  <si>
-    <t>CLAUDIA</t>
   </si>
 </sst>
 </file>
@@ -805,7 +796,7 @@
         <v>10</v>
       </c>
       <c r="T4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U4">
         <v>10</v>
@@ -894,7 +885,7 @@
         <v>8</v>
       </c>
       <c r="T5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U5">
         <v>5</v>
@@ -983,7 +974,7 @@
         <v>5</v>
       </c>
       <c r="T6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U6">
         <v>5</v>
@@ -1072,7 +1063,7 @@
         <v>9</v>
       </c>
       <c r="T7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U7">
         <v>6</v>
@@ -1093,7 +1084,7 @@
         <v>9</v>
       </c>
       <c r="AA7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB7">
         <v>6</v>
@@ -1161,7 +1152,7 @@
         <v>8</v>
       </c>
       <c r="T8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U8">
         <v>5</v>
@@ -1250,7 +1241,7 @@
         <v>10</v>
       </c>
       <c r="T9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U9">
         <v>10</v>
@@ -1339,7 +1330,7 @@
         <v>5</v>
       </c>
       <c r="T10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U10">
         <v>6</v>
@@ -1360,7 +1351,7 @@
         <v>5</v>
       </c>
       <c r="AA10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB10">
         <v>6</v>
@@ -1428,7 +1419,7 @@
         <v>9</v>
       </c>
       <c r="T11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U11">
         <v>10</v>
@@ -1517,7 +1508,7 @@
         <v>5</v>
       </c>
       <c r="T12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U12">
         <v>5</v>
@@ -1606,7 +1597,7 @@
         <v>9</v>
       </c>
       <c r="T13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U13">
         <v>10</v>
@@ -1695,7 +1686,7 @@
         <v>5</v>
       </c>
       <c r="T14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U14">
         <v>5</v>
@@ -1716,7 +1707,7 @@
         <v>5</v>
       </c>
       <c r="AA14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB14">
         <v>5</v>
@@ -1784,7 +1775,7 @@
         <v>10</v>
       </c>
       <c r="T15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U15">
         <v>6</v>
@@ -1873,7 +1864,7 @@
         <v>8</v>
       </c>
       <c r="T16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U16">
         <v>5</v>
@@ -1962,7 +1953,7 @@
         <v>8</v>
       </c>
       <c r="T17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U17">
         <v>7</v>
@@ -1983,7 +1974,7 @@
         <v>8</v>
       </c>
       <c r="AA17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB17">
         <v>6</v>
@@ -2045,7 +2036,7 @@
         <v>5</v>
       </c>
       <c r="T18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V18">
         <v>0</v>
@@ -2128,7 +2119,7 @@
         <v>7</v>
       </c>
       <c r="T19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U19">
         <v>7</v>
@@ -2217,7 +2208,7 @@
         <v>5</v>
       </c>
       <c r="T20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U20">
         <v>5</v>
@@ -2238,7 +2229,7 @@
         <v>5</v>
       </c>
       <c r="AA20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB20">
         <v>5</v>
@@ -2306,7 +2297,7 @@
         <v>5</v>
       </c>
       <c r="T21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U21">
         <v>7</v>
@@ -2327,7 +2318,7 @@
         <v>6</v>
       </c>
       <c r="AA21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB21">
         <v>5</v>
@@ -2395,7 +2386,7 @@
         <v>5</v>
       </c>
       <c r="T22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U22">
         <v>5</v>
@@ -2484,7 +2475,7 @@
         <v>5</v>
       </c>
       <c r="T23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U23">
         <v>6</v>
@@ -2505,7 +2496,7 @@
         <v>5</v>
       </c>
       <c r="AA23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB23">
         <v>6</v>
@@ -2573,7 +2564,7 @@
         <v>8</v>
       </c>
       <c r="T24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U24">
         <v>10</v>
@@ -2662,7 +2653,7 @@
         <v>7</v>
       </c>
       <c r="T25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U25">
         <v>5</v>
@@ -2751,7 +2742,7 @@
         <v>10</v>
       </c>
       <c r="T26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U26">
         <v>9</v>
@@ -2772,7 +2763,7 @@
         <v>10</v>
       </c>
       <c r="AA26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB26">
         <v>7</v>
@@ -2840,7 +2831,7 @@
         <v>5</v>
       </c>
       <c r="T27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U27">
         <v>5</v>
@@ -2861,7 +2852,7 @@
         <v>6</v>
       </c>
       <c r="AA27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB27">
         <v>6</v>
@@ -2929,7 +2920,7 @@
         <v>5</v>
       </c>
       <c r="T28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U28">
         <v>5</v>
@@ -3208,7 +3199,7 @@
         <v>83</v>
       </c>
       <c r="T5">
-        <v>93.2</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="U5">
         <v>95</v>
@@ -3276,7 +3267,7 @@
         <v>36.6</v>
       </c>
       <c r="T6">
-        <v>68.2</v>
+        <v>46.9</v>
       </c>
       <c r="U6">
         <v>30</v>
@@ -3344,7 +3335,7 @@
         <v>88.40000000000001</v>
       </c>
       <c r="T7">
-        <v>79.5</v>
+        <v>82.8</v>
       </c>
       <c r="U7">
         <v>95</v>
@@ -3412,7 +3403,7 @@
         <v>69.59999999999999</v>
       </c>
       <c r="T8">
-        <v>75</v>
+        <v>82.8</v>
       </c>
       <c r="U8">
         <v>73.3</v>
@@ -3480,7 +3471,7 @@
         <v>99.09999999999999</v>
       </c>
       <c r="T9">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="U9">
         <v>98.3</v>
@@ -3548,7 +3539,7 @@
         <v>70.5</v>
       </c>
       <c r="T10">
-        <v>79.5</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="U10">
         <v>85</v>
@@ -3616,7 +3607,7 @@
         <v>97.3</v>
       </c>
       <c r="T11">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="U11">
         <v>100</v>
@@ -3684,7 +3675,7 @@
         <v>53.6</v>
       </c>
       <c r="T12">
-        <v>77.3</v>
+        <v>53.1</v>
       </c>
       <c r="U12">
         <v>53.3</v>
@@ -3752,7 +3743,7 @@
         <v>99.09999999999999</v>
       </c>
       <c r="T13">
-        <v>93.2</v>
+        <v>95.3</v>
       </c>
       <c r="U13">
         <v>91.7</v>
@@ -3820,7 +3811,7 @@
         <v>71.40000000000001</v>
       </c>
       <c r="T14">
-        <v>77.3</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="U14">
         <v>85</v>
@@ -3888,7 +3879,7 @@
         <v>92.90000000000001</v>
       </c>
       <c r="T15">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="U15">
         <v>100</v>
@@ -3956,7 +3947,7 @@
         <v>82.09999999999999</v>
       </c>
       <c r="T16">
-        <v>88.59999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="U16">
         <v>78.3</v>
@@ -4024,7 +4015,7 @@
         <v>94.59999999999999</v>
       </c>
       <c r="T17">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="U17">
         <v>91.7</v>
@@ -4151,7 +4142,7 @@
         <v>93.8</v>
       </c>
       <c r="T19">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="U19">
         <v>91.7</v>
@@ -4219,7 +4210,7 @@
         <v>75</v>
       </c>
       <c r="T20">
-        <v>70.5</v>
+        <v>82.8</v>
       </c>
       <c r="U20">
         <v>75</v>
@@ -4287,7 +4278,7 @@
         <v>82.09999999999999</v>
       </c>
       <c r="T21">
-        <v>70.5</v>
+        <v>82.8</v>
       </c>
       <c r="U21">
         <v>78.3</v>
@@ -4355,7 +4346,7 @@
         <v>72.3</v>
       </c>
       <c r="T22">
-        <v>68.2</v>
+        <v>62.5</v>
       </c>
       <c r="U22">
         <v>66.7</v>
@@ -4423,7 +4414,7 @@
         <v>68.8</v>
       </c>
       <c r="T23">
-        <v>79.5</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="U23">
         <v>81.7</v>
@@ -4491,7 +4482,7 @@
         <v>83.90000000000001</v>
       </c>
       <c r="T24">
-        <v>88.59999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="U24">
         <v>93.3</v>
@@ -4559,7 +4550,7 @@
         <v>86.59999999999999</v>
       </c>
       <c r="T25">
-        <v>93.2</v>
+        <v>92.2</v>
       </c>
       <c r="U25">
         <v>85</v>
@@ -4627,7 +4618,7 @@
         <v>96.40000000000001</v>
       </c>
       <c r="T26">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="U26">
         <v>100</v>
@@ -4695,7 +4686,7 @@
         <v>83</v>
       </c>
       <c r="T27">
-        <v>93.2</v>
+        <v>95.3</v>
       </c>
       <c r="U27">
         <v>96.7</v>
@@ -4763,7 +4754,7 @@
         <v>48.2</v>
       </c>
       <c r="T28">
-        <v>86.40000000000001</v>
+        <v>75</v>
       </c>
       <c r="U28">
         <v>76.7</v>
@@ -4826,25 +4817,25 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
         <v>50</v>
       </c>
       <c r="C2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D2">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E2">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F2" s="2">
-        <v>32</v>
+        <v>54.2</v>
       </c>
       <c r="G2" s="2">
-        <v>68</v>
+        <v>45.8</v>
       </c>
       <c r="H2">
         <v>6.1</v>
@@ -4858,28 +4849,28 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
         <v>51</v>
       </c>
       <c r="C3">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D3">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E3">
         <v>11</v>
       </c>
       <c r="F3" s="2">
-        <v>54.2</v>
+        <v>56</v>
       </c>
       <c r="G3" s="2">
-        <v>45.8</v>
+        <v>44</v>
       </c>
       <c r="H3">
-        <v>6.1</v>
+        <v>6.8</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -4890,7 +4881,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
         <v>52</v>
@@ -4899,19 +4890,19 @@
         <v>25</v>
       </c>
       <c r="D4">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E4">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F4" s="2">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="G4" s="2">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="H4">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -4922,7 +4913,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>53</v>
@@ -4943,7 +4934,7 @@
         <v>40</v>
       </c>
       <c r="H5">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4954,7 +4945,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
         <v>54</v>
@@ -4975,7 +4966,7 @@
         <v>40</v>
       </c>
       <c r="H6">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4986,7 +4977,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
         <v>55</v>
@@ -4995,19 +4986,19 @@
         <v>25</v>
       </c>
       <c r="D7">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F7" s="2">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="G7" s="2">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="H7">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -5089,7 +5080,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5127,16 +5118,16 @@
         <v>61</v>
       </c>
       <c r="C2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -5150,16 +5141,16 @@
         <v>61</v>
       </c>
       <c r="C3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -5173,16 +5164,16 @@
         <v>62</v>
       </c>
       <c r="C4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D4" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -5196,16 +5187,16 @@
         <v>62</v>
       </c>
       <c r="C5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -5213,22 +5204,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920152</v>
+        <v>21330051920125</v>
       </c>
       <c r="B6" t="s">
         <v>63</v>
       </c>
       <c r="C6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D6" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E6" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -5236,22 +5227,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920152</v>
+        <v>21330051920125</v>
       </c>
       <c r="B7" t="s">
         <v>63</v>
       </c>
       <c r="C7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D7" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F7" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -5259,47 +5250,24 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920114</v>
+        <v>20330051920152</v>
       </c>
       <c r="B8" t="s">
         <v>64</v>
       </c>
       <c r="C8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E8" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>21330051920122</v>
-      </c>
-      <c r="B9" t="s">
-        <v>65</v>
-      </c>
-      <c r="C9" t="s">
-        <v>70</v>
-      </c>
-      <c r="D9" t="s">
-        <v>75</v>
-      </c>
-      <c r="E9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" t="s">
-        <v>50</v>
-      </c>
-      <c r="G9">
         <v>5</v>
       </c>
     </row>
